--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/before_conversion_alps_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/before_conversion_alps_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="452">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Euganei (Euganean geothermal area - Battaglia Terme)</t>
@@ -1730,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD312"/>
+  <dimension ref="A1:AE312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1758,9 +1761,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1851,13 +1855,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C2">
         <v>45.28444444</v>
@@ -1875,12 +1882,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C3">
         <v>45.28694444</v>
@@ -1898,12 +1905,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C4">
         <v>45.285</v>
@@ -1921,12 +1928,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5">
         <v>45.29583333</v>
@@ -1944,12 +1951,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C6">
         <v>44.6916766</v>
@@ -1967,12 +1974,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C7">
         <v>46.492436</v>
@@ -2011,12 +2018,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C8">
         <v>46.49255</v>
@@ -2034,12 +2041,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C9">
         <v>46.492495</v>
@@ -2078,12 +2085,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10">
         <v>46.492144</v>
@@ -2122,12 +2129,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11">
         <v>46.49282</v>
@@ -2145,12 +2152,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C12">
         <v>46.492916</v>
@@ -2168,12 +2175,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C13">
         <v>46.49119</v>
@@ -2191,12 +2198,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C14">
         <v>46.490844</v>
@@ -2235,12 +2242,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C15">
         <v>46.490823</v>
@@ -2279,12 +2286,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C16">
         <v>46.491967</v>
@@ -2325,10 +2332,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C17">
         <v>46.04222222</v>
@@ -2348,10 +2355,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18">
         <v>45.7575</v>
@@ -2374,10 +2381,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19">
         <v>46.14638889</v>
@@ -2397,10 +2404,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C20">
         <v>46.1968</v>
@@ -2453,10 +2460,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21">
         <v>46.20346</v>
@@ -2476,10 +2483,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22">
         <v>46.09804000000001</v>
@@ -2499,10 +2506,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C23">
         <v>46.30727</v>
@@ -2522,10 +2529,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C24">
         <v>46.23795</v>
@@ -2545,10 +2552,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C25">
         <v>46.24898</v>
@@ -2568,10 +2575,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C26">
         <v>46.19984</v>
@@ -2591,10 +2598,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C27">
         <v>46.20199</v>
@@ -2614,10 +2621,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C28">
         <v>46.26364</v>
@@ -2637,10 +2644,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C29">
         <v>46.29705</v>
@@ -2660,10 +2667,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C30">
         <v>46.31316</v>
@@ -2683,10 +2690,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C31">
         <v>46.20013</v>
@@ -2706,10 +2713,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C32">
         <v>46.24352</v>
@@ -2759,10 +2766,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C33">
         <v>45.76189</v>
@@ -2815,10 +2822,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C34">
         <v>45.85138889</v>
@@ -2838,10 +2845,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C35">
         <v>45.85138889</v>
@@ -2861,10 +2868,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C36">
         <v>45.85138889</v>
@@ -2884,10 +2891,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C37">
         <v>46.26274</v>
@@ -2937,10 +2944,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C38">
         <v>46.26274</v>
@@ -2993,10 +3000,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C39">
         <v>45.500093</v>
@@ -3016,10 +3023,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C40">
         <v>44.20638889</v>
@@ -3069,10 +3076,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C41">
         <v>44.20638889</v>
@@ -3092,10 +3099,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C42">
         <v>44.20638889</v>
@@ -3115,10 +3122,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C43">
         <v>44.20638889</v>
@@ -3168,10 +3175,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C44">
         <v>44.20638889</v>
@@ -3215,10 +3222,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C45">
         <v>44.28861111</v>
@@ -3268,10 +3275,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C46">
         <v>44.28861111</v>
@@ -3291,10 +3298,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C47">
         <v>44.28861111</v>
@@ -3338,10 +3345,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C48">
         <v>44.28861111</v>
@@ -3391,10 +3398,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C49">
         <v>44.28861111</v>
@@ -3444,10 +3451,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C50">
         <v>44.28861111</v>
@@ -3467,10 +3474,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C51">
         <v>44.28861111</v>
@@ -3490,10 +3497,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C52">
         <v>44.66305556</v>
@@ -3513,10 +3520,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C53">
         <v>44.67527778</v>
@@ -3560,10 +3567,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C54">
         <v>44.66305556</v>
@@ -3583,10 +3590,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C55">
         <v>44.7</v>
@@ -3636,10 +3643,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C56">
         <v>44.6333333</v>
@@ -3689,10 +3696,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C57">
         <v>44.6333333</v>
@@ -3742,10 +3749,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C58">
         <v>44.6666667</v>
@@ -3795,10 +3802,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C59">
         <v>44.5833333</v>
@@ -3848,10 +3855,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C60">
         <v>44.6833333</v>
@@ -3901,10 +3908,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C61">
         <v>44.6833333</v>
@@ -3954,10 +3961,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C62">
         <v>44.6833333</v>
@@ -4007,10 +4014,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C63">
         <v>44.3572222</v>
@@ -4057,10 +4064,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B64" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C64">
         <v>44.7</v>
@@ -4110,10 +4117,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C65">
         <v>44.6833333</v>
@@ -4163,10 +4170,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C66">
         <v>46.042222</v>
@@ -4186,10 +4193,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C67">
         <v>44.661944</v>
@@ -4209,10 +4216,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C68">
         <v>45.368333</v>
@@ -4232,10 +4239,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C69">
         <v>45.276667</v>
@@ -4255,10 +4262,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C70">
         <v>45.268889</v>
@@ -4278,10 +4285,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C71">
         <v>45.264444</v>
@@ -4301,10 +4308,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C72">
         <v>45.4</v>
@@ -4324,10 +4331,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C73">
         <v>45.447222</v>
@@ -4350,10 +4357,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C74">
         <v>45.402222</v>
@@ -4373,10 +4380,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C75">
         <v>45.396944</v>
@@ -4396,10 +4403,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C76">
         <v>45.408889</v>
@@ -4419,10 +4426,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C77">
         <v>45.408889</v>
@@ -4445,10 +4452,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C78">
         <v>45.307222</v>
@@ -4468,10 +4475,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B79" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C79">
         <v>45.256944</v>
@@ -4491,10 +4498,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C80">
         <v>45.408889</v>
@@ -4514,10 +4521,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C81">
         <v>45.396667</v>
@@ -4537,7 +4544,7 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C82">
         <v>45.773644</v>
@@ -4581,10 +4588,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C83">
         <v>46.45469</v>
@@ -4634,10 +4641,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C84">
         <v>46.45469</v>
@@ -4684,10 +4691,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B85" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C85">
         <v>46.45469</v>
@@ -4734,10 +4741,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C86">
         <v>46.6129</v>
@@ -4787,10 +4794,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C87">
         <v>46.9693</v>
@@ -4843,7 +4850,7 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C88">
         <v>46.61848</v>
@@ -4884,7 +4891,7 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C89">
         <v>46.08115</v>
@@ -4937,10 +4944,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C90">
         <v>46.30173</v>
@@ -4993,10 +5000,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C91">
         <v>46.30225</v>
@@ -5049,10 +5056,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C92">
         <v>46.18651</v>
@@ -5105,10 +5112,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B93" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C93">
         <v>46.18736</v>
@@ -5161,10 +5168,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C94">
         <v>46.5627</v>
@@ -5214,10 +5221,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C95">
         <v>46.2077</v>
@@ -5261,10 +5268,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C96">
         <v>46.38643</v>
@@ -5317,10 +5324,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C97">
         <v>46.38173</v>
@@ -5373,10 +5380,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C98">
         <v>46.3815</v>
@@ -5429,10 +5436,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C99">
         <v>46.38397</v>
@@ -5485,10 +5492,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B100" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C100">
         <v>46.37746</v>
@@ -5541,10 +5548,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C101">
         <v>46.37881</v>
@@ -5597,10 +5604,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B102" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C102">
         <v>46.18258</v>
@@ -5653,10 +5660,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B103" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C103">
         <v>46.71674</v>
@@ -5706,10 +5713,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B104" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C104">
         <v>45.7630254</v>
@@ -5759,10 +5766,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C105">
         <v>46.7729</v>
@@ -5818,10 +5825,10 @@
     </row>
     <row r="106" spans="1:30">
       <c r="A106" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B106" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C106">
         <v>46.76984</v>
@@ -5871,10 +5878,10 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B107" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C107">
         <v>46.14504</v>
@@ -5930,10 +5937,10 @@
     </row>
     <row r="108" spans="1:30">
       <c r="A108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C108">
         <v>46.6875</v>
@@ -5983,10 +5990,10 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B109" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C109">
         <v>46.20722</v>
@@ -6039,10 +6046,10 @@
     </row>
     <row r="110" spans="1:30">
       <c r="A110" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B110" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C110">
         <v>46.20722</v>
@@ -6095,10 +6102,10 @@
     </row>
     <row r="111" spans="1:30">
       <c r="A111" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C111">
         <v>46.07518</v>
@@ -6151,10 +6158,10 @@
     </row>
     <row r="112" spans="1:30">
       <c r="A112" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B112" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C112">
         <v>46.622011</v>
@@ -6207,10 +6214,10 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B113" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C113">
         <v>46.1510041</v>
@@ -6263,10 +6270,10 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B114" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C114">
         <v>46.07655436</v>
@@ -6319,10 +6326,10 @@
     </row>
     <row r="115" spans="1:30">
       <c r="A115" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C115">
         <v>47.00229052</v>
@@ -6342,10 +6349,10 @@
     </row>
     <row r="116" spans="1:30">
       <c r="A116" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C116">
         <v>47.36492038</v>
@@ -6365,10 +6372,10 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B117" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C117">
         <v>48.008769</v>
@@ -6424,10 +6431,10 @@
     </row>
     <row r="118" spans="1:30">
       <c r="A118" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B118" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C118">
         <v>48.008769</v>
@@ -6480,10 +6487,10 @@
     </row>
     <row r="119" spans="1:30">
       <c r="A119" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B119" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C119">
         <v>48.008769</v>
@@ -6533,10 +6540,10 @@
     </row>
     <row r="120" spans="1:30">
       <c r="A120" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B120" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C120">
         <v>48.008769</v>
@@ -6586,10 +6593,10 @@
     </row>
     <row r="121" spans="1:30">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C121">
         <v>48.008769</v>
@@ -6639,10 +6646,10 @@
     </row>
     <row r="122" spans="1:30">
       <c r="A122" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B122" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C122">
         <v>48.008769</v>
@@ -6692,10 +6699,10 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B123" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C123">
         <v>48.008769</v>
@@ -6742,10 +6749,10 @@
     </row>
     <row r="124" spans="1:30">
       <c r="A124" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B124" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C124">
         <v>48.008769</v>
@@ -6795,10 +6802,10 @@
     </row>
     <row r="125" spans="1:30">
       <c r="A125" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B125" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C125">
         <v>47.772023</v>
@@ -6848,10 +6855,10 @@
     </row>
     <row r="126" spans="1:30">
       <c r="A126" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B126" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C126">
         <v>47.967323</v>
@@ -6901,10 +6908,10 @@
     </row>
     <row r="127" spans="1:30">
       <c r="A127" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B127" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C127">
         <v>47.8321</v>
@@ -6957,10 +6964,10 @@
     </row>
     <row r="128" spans="1:30">
       <c r="A128" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B128" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C128">
         <v>47.1145</v>
@@ -6998,10 +7005,10 @@
     </row>
     <row r="129" spans="1:30">
       <c r="A129" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B129" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C129">
         <v>47.1145</v>
@@ -7039,10 +7046,10 @@
     </row>
     <row r="130" spans="1:30">
       <c r="A130" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B130" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C130">
         <v>47.1145</v>
@@ -7080,10 +7087,10 @@
     </row>
     <row r="131" spans="1:30">
       <c r="A131" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B131" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C131">
         <v>47.1145</v>
@@ -7121,10 +7128,10 @@
     </row>
     <row r="132" spans="1:30">
       <c r="A132" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B132" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C132">
         <v>47.1149</v>
@@ -7165,10 +7172,10 @@
     </row>
     <row r="133" spans="1:30">
       <c r="A133" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B133" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C133">
         <v>47.1149</v>
@@ -7209,10 +7216,10 @@
     </row>
     <row r="134" spans="1:30">
       <c r="A134" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B134" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C134">
         <v>47.1149</v>
@@ -7253,10 +7260,10 @@
     </row>
     <row r="135" spans="1:30">
       <c r="A135" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B135" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C135">
         <v>47.1149</v>
@@ -7297,10 +7304,10 @@
     </row>
     <row r="136" spans="1:30">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B136" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C136">
         <v>47.1149</v>
@@ -7341,10 +7348,10 @@
     </row>
     <row r="137" spans="1:30">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C137">
         <v>47.1149</v>
@@ -7385,10 +7392,10 @@
     </row>
     <row r="138" spans="1:30">
       <c r="A138" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B138" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C138">
         <v>47.1149</v>
@@ -7429,10 +7436,10 @@
     </row>
     <row r="139" spans="1:30">
       <c r="A139" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B139" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C139">
         <v>47.1149</v>
@@ -7473,10 +7480,10 @@
     </row>
     <row r="140" spans="1:30">
       <c r="A140" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B140" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C140">
         <v>47.1149</v>
@@ -7529,10 +7536,10 @@
     </row>
     <row r="141" spans="1:30">
       <c r="A141" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B141" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C141">
         <v>47.1149</v>
@@ -7588,10 +7595,10 @@
     </row>
     <row r="142" spans="1:30">
       <c r="A142" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B142" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C142">
         <v>47.1149</v>
@@ -7647,10 +7654,10 @@
     </row>
     <row r="143" spans="1:30">
       <c r="A143" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B143" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C143">
         <v>46.9803</v>
@@ -7700,10 +7707,10 @@
     </row>
     <row r="144" spans="1:30">
       <c r="A144" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B144" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C144">
         <v>46.9803</v>
@@ -7753,10 +7760,10 @@
     </row>
     <row r="145" spans="1:30">
       <c r="A145" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B145" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C145">
         <v>46.5886</v>
@@ -7800,10 +7807,10 @@
     </row>
     <row r="146" spans="1:30">
       <c r="A146" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C146">
         <v>46.5886</v>
@@ -7823,10 +7830,10 @@
     </row>
     <row r="147" spans="1:30">
       <c r="A147" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B147" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C147">
         <v>46.5886</v>
@@ -7876,10 +7883,10 @@
     </row>
     <row r="148" spans="1:30">
       <c r="A148" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B148" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C148">
         <v>46.5886</v>
@@ -7899,10 +7906,10 @@
     </row>
     <row r="149" spans="1:30">
       <c r="A149" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B149" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C149">
         <v>46.5886</v>
@@ -7952,10 +7959,10 @@
     </row>
     <row r="150" spans="1:30">
       <c r="A150" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B150" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C150">
         <v>46.5886</v>
@@ -8005,10 +8012,10 @@
     </row>
     <row r="151" spans="1:30">
       <c r="A151" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B151" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C151">
         <v>46.5886</v>
@@ -8058,10 +8065,10 @@
     </row>
     <row r="152" spans="1:30">
       <c r="A152" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B152" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C152">
         <v>46.5886</v>
@@ -8111,7 +8118,7 @@
     </row>
     <row r="153" spans="1:30">
       <c r="A153" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C153">
         <v>47.1422</v>
@@ -8152,7 +8159,7 @@
     </row>
     <row r="154" spans="1:30">
       <c r="A154" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C154">
         <v>47.9261</v>
@@ -8205,7 +8212,7 @@
     </row>
     <row r="155" spans="1:30">
       <c r="A155" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C155">
         <v>47.9739</v>
@@ -8249,10 +8256,10 @@
     </row>
     <row r="156" spans="1:30">
       <c r="A156" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B156" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C156">
         <v>47.7195</v>
@@ -8272,10 +8279,10 @@
     </row>
     <row r="157" spans="1:30">
       <c r="A157" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B157" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C157">
         <v>47.743516</v>
@@ -8328,10 +8335,10 @@
     </row>
     <row r="158" spans="1:30">
       <c r="A158" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B158" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C158">
         <v>47.719742</v>
@@ -8387,10 +8394,10 @@
     </row>
     <row r="159" spans="1:30">
       <c r="A159" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B159" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C159">
         <v>47.7338</v>
@@ -8431,10 +8438,10 @@
     </row>
     <row r="160" spans="1:30">
       <c r="A160" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B160" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C160">
         <v>47.582</v>
@@ -8484,10 +8491,10 @@
     </row>
     <row r="161" spans="1:30">
       <c r="A161" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B161" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C161">
         <v>47.582</v>
@@ -8540,7 +8547,7 @@
     </row>
     <row r="162" spans="1:30">
       <c r="A162" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C162">
         <v>47.3367</v>
@@ -8587,7 +8594,7 @@
     </row>
     <row r="163" spans="1:30">
       <c r="A163" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C163">
         <v>47.3491</v>
@@ -8628,7 +8635,7 @@
     </row>
     <row r="164" spans="1:30">
       <c r="A164" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C164">
         <v>47.4213</v>
@@ -8666,7 +8673,7 @@
     </row>
     <row r="165" spans="1:30">
       <c r="A165" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C165">
         <v>47.1795</v>
@@ -8710,7 +8717,7 @@
     </row>
     <row r="166" spans="1:30">
       <c r="A166" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C166">
         <v>47.0951</v>
@@ -8748,7 +8755,7 @@
     </row>
     <row r="167" spans="1:30">
       <c r="A167" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C167">
         <v>47.5511</v>
@@ -8795,10 +8802,10 @@
     </row>
     <row r="168" spans="1:30">
       <c r="A168" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B168" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C168">
         <v>47.2091</v>
@@ -8854,10 +8861,10 @@
     </row>
     <row r="169" spans="1:30">
       <c r="A169" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B169" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C169">
         <v>47.2091</v>
@@ -8910,10 +8917,10 @@
     </row>
     <row r="170" spans="1:30">
       <c r="A170" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B170" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C170">
         <v>46.9275</v>
@@ -8951,10 +8958,10 @@
     </row>
     <row r="171" spans="1:30">
       <c r="A171" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B171" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C171">
         <v>46.9275</v>
@@ -9001,10 +9008,10 @@
     </row>
     <row r="172" spans="1:30">
       <c r="A172" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B172" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C172">
         <v>47.065</v>
@@ -9045,10 +9052,10 @@
     </row>
     <row r="173" spans="1:30">
       <c r="A173" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B173" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C173">
         <v>47.065</v>
@@ -9086,10 +9093,10 @@
     </row>
     <row r="174" spans="1:30">
       <c r="A174" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B174" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C174">
         <v>46.4869</v>
@@ -9124,7 +9131,7 @@
     </row>
     <row r="175" spans="1:30">
       <c r="A175" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C175">
         <v>46.7236</v>
@@ -9162,10 +9169,10 @@
     </row>
     <row r="176" spans="1:30">
       <c r="A176" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B176" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C176">
         <v>46.9887</v>
@@ -9212,10 +9219,10 @@
     </row>
     <row r="177" spans="1:30">
       <c r="A177" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B177" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C177">
         <v>46.9887</v>
@@ -9262,10 +9269,10 @@
     </row>
     <row r="178" spans="1:30">
       <c r="A178" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B178" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C178">
         <v>46.8892</v>
@@ -9315,7 +9322,7 @@
     </row>
     <row r="179" spans="1:30">
       <c r="A179" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C179">
         <v>46.902</v>
@@ -9353,10 +9360,10 @@
     </row>
     <row r="180" spans="1:30">
       <c r="A180" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B180" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C180">
         <v>47.0784</v>
@@ -9409,10 +9416,10 @@
     </row>
     <row r="181" spans="1:30">
       <c r="A181" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B181" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C181">
         <v>47.0761</v>
@@ -9465,7 +9472,7 @@
     </row>
     <row r="182" spans="1:30">
       <c r="A182" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C182">
         <v>47.2412</v>
@@ -9506,7 +9513,7 @@
     </row>
     <row r="183" spans="1:30">
       <c r="A183" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C183">
         <v>47.3718</v>
@@ -9544,7 +9551,7 @@
     </row>
     <row r="184" spans="1:30">
       <c r="A184" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C184">
         <v>46.6735</v>
@@ -9582,7 +9589,7 @@
     </row>
     <row r="185" spans="1:30">
       <c r="A185" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C185">
         <v>47.3681</v>
@@ -9635,10 +9642,10 @@
     </row>
     <row r="186" spans="1:30">
       <c r="A186" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B186" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C186">
         <v>47.022549</v>
@@ -9694,10 +9701,10 @@
     </row>
     <row r="187" spans="1:30">
       <c r="A187" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B187" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C187">
         <v>47.022549</v>
@@ -9747,10 +9754,10 @@
     </row>
     <row r="188" spans="1:30">
       <c r="A188" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B188" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C188">
         <v>47.022549</v>
@@ -9806,10 +9813,10 @@
     </row>
     <row r="189" spans="1:30">
       <c r="A189" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B189" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C189">
         <v>47.022549</v>
@@ -9865,10 +9872,10 @@
     </row>
     <row r="190" spans="1:30">
       <c r="A190" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B190" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C190">
         <v>47.022549</v>
@@ -9921,10 +9928,10 @@
     </row>
     <row r="191" spans="1:30">
       <c r="A191" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B191" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C191">
         <v>48.031542</v>
@@ -9947,10 +9954,10 @@
     </row>
     <row r="192" spans="1:30">
       <c r="A192" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B192" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C192">
         <v>47.66422</v>
@@ -10003,10 +10010,10 @@
     </row>
     <row r="193" spans="1:30">
       <c r="A193" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B193" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C193">
         <v>47.668206</v>
@@ -10059,10 +10066,10 @@
     </row>
     <row r="194" spans="1:30">
       <c r="A194" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B194" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C194">
         <v>47.611275</v>
@@ -10115,10 +10122,10 @@
     </row>
     <row r="195" spans="1:30">
       <c r="A195" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B195" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C195">
         <v>47.510362</v>
@@ -10174,10 +10181,10 @@
     </row>
     <row r="196" spans="1:30">
       <c r="A196" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B196" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C196">
         <v>46.816876</v>
@@ -10227,10 +10234,10 @@
     </row>
     <row r="197" spans="1:30">
       <c r="A197" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B197" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C197">
         <v>47.311421</v>
@@ -10277,10 +10284,10 @@
     </row>
     <row r="198" spans="1:30">
       <c r="A198" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B198" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C198">
         <v>47.907481</v>
@@ -10342,10 +10349,10 @@
     </row>
     <row r="199" spans="1:30">
       <c r="A199" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B199" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C199">
         <v>47.833372</v>
@@ -10395,10 +10402,10 @@
     </row>
     <row r="200" spans="1:30">
       <c r="A200" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B200" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C200">
         <v>47.619332</v>
@@ -10457,10 +10464,10 @@
     </row>
     <row r="201" spans="1:30">
       <c r="A201" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B201" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C201">
         <v>47.772905</v>
@@ -10513,10 +10520,10 @@
     </row>
     <row r="202" spans="1:30">
       <c r="A202" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B202" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C202">
         <v>47.446304</v>
@@ -10572,10 +10579,10 @@
     </row>
     <row r="203" spans="1:30">
       <c r="A203" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B203" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C203">
         <v>47.446304</v>
@@ -10634,10 +10641,10 @@
     </row>
     <row r="204" spans="1:30">
       <c r="A204" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B204" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C204">
         <v>47.332869</v>
@@ -10699,10 +10706,10 @@
     </row>
     <row r="205" spans="1:30">
       <c r="A205" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B205" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C205">
         <v>46.92752</v>
@@ -10755,10 +10762,10 @@
     </row>
     <row r="206" spans="1:30">
       <c r="A206" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B206" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C206">
         <v>46.894354</v>
@@ -10811,10 +10818,10 @@
     </row>
     <row r="207" spans="1:30">
       <c r="A207" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B207" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C207">
         <v>46.950836</v>
@@ -10861,10 +10868,10 @@
     </row>
     <row r="208" spans="1:30">
       <c r="A208" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B208" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C208">
         <v>46.96412</v>
@@ -10914,10 +10921,10 @@
     </row>
     <row r="209" spans="1:30">
       <c r="A209" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B209" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C209">
         <v>47.016095</v>
@@ -10970,10 +10977,10 @@
     </row>
     <row r="210" spans="1:30">
       <c r="A210" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B210" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C210">
         <v>46.478632</v>
@@ -11026,10 +11033,10 @@
     </row>
     <row r="211" spans="1:30">
       <c r="A211" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B211" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C211">
         <v>46.478632</v>
@@ -11082,10 +11089,10 @@
     </row>
     <row r="212" spans="1:30">
       <c r="A212" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B212" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C212">
         <v>46.475592</v>
@@ -11135,10 +11142,10 @@
     </row>
     <row r="213" spans="1:30">
       <c r="A213" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B213" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C213">
         <v>46.425898</v>
@@ -11188,10 +11195,10 @@
     </row>
     <row r="214" spans="1:30">
       <c r="A214" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B214" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C214">
         <v>46.425898</v>
@@ -11241,10 +11248,10 @@
     </row>
     <row r="215" spans="1:30">
       <c r="A215" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B215" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C215">
         <v>46.42049</v>
@@ -11297,10 +11304,10 @@
     </row>
     <row r="216" spans="1:30">
       <c r="A216" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B216" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C216">
         <v>46.42049</v>
@@ -11356,10 +11363,10 @@
     </row>
     <row r="217" spans="1:30">
       <c r="A217" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B217" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C217">
         <v>46.425654</v>
@@ -11406,10 +11413,10 @@
     </row>
     <row r="218" spans="1:30">
       <c r="A218" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B218" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C218">
         <v>46.740152</v>
@@ -11456,10 +11463,10 @@
     </row>
     <row r="219" spans="1:30">
       <c r="A219" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B219" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C219">
         <v>46.737775</v>
@@ -11515,10 +11522,10 @@
     </row>
     <row r="220" spans="1:30">
       <c r="A220" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B220" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C220">
         <v>46.667161</v>
@@ -11574,10 +11581,10 @@
     </row>
     <row r="221" spans="1:30">
       <c r="A221" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B221" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C221">
         <v>46.72917800000001</v>
@@ -11633,10 +11640,10 @@
     </row>
     <row r="222" spans="1:30">
       <c r="A222" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B222" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C222">
         <v>46.726966</v>
@@ -11692,10 +11699,10 @@
     </row>
     <row r="223" spans="1:30">
       <c r="A223" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B223" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C223">
         <v>46.722534</v>
@@ -11751,10 +11758,10 @@
     </row>
     <row r="224" spans="1:30">
       <c r="A224" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B224" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C224">
         <v>46.883205</v>
@@ -11804,10 +11811,10 @@
     </row>
     <row r="225" spans="1:30">
       <c r="A225" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B225" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C225">
         <v>46.905769</v>
@@ -11860,10 +11867,10 @@
     </row>
     <row r="226" spans="1:30">
       <c r="A226" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B226" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C226">
         <v>46.814254</v>
@@ -11916,10 +11923,10 @@
     </row>
     <row r="227" spans="1:30">
       <c r="A227" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B227" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C227">
         <v>47.987145</v>
@@ -11981,10 +11988,10 @@
     </row>
     <row r="228" spans="1:30">
       <c r="A228" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B228" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C228">
         <v>47.987145</v>
@@ -12046,10 +12053,10 @@
     </row>
     <row r="229" spans="1:30">
       <c r="A229" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B229" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C229">
         <v>47.987145</v>
@@ -12111,10 +12118,10 @@
     </row>
     <row r="230" spans="1:30">
       <c r="A230" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B230" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C230">
         <v>47.42863300000001</v>
@@ -12173,10 +12180,10 @@
     </row>
     <row r="231" spans="1:30">
       <c r="A231" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B231" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C231">
         <v>47.133327</v>
@@ -12223,10 +12230,10 @@
     </row>
     <row r="232" spans="1:30">
       <c r="A232" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B232" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C232">
         <v>47.287951</v>
@@ -12279,10 +12286,10 @@
     </row>
     <row r="233" spans="1:30">
       <c r="A233" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B233" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C233">
         <v>46.919494</v>
@@ -12329,10 +12336,10 @@
     </row>
     <row r="234" spans="1:30">
       <c r="A234" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B234" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C234">
         <v>47.473067</v>
@@ -12391,10 +12398,10 @@
     </row>
     <row r="235" spans="1:30">
       <c r="A235" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B235" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C235">
         <v>47.472165</v>
@@ -12450,10 +12457,10 @@
     </row>
     <row r="236" spans="1:30">
       <c r="A236" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B236" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C236">
         <v>47.361698</v>
@@ -12506,10 +12513,10 @@
     </row>
     <row r="237" spans="1:30">
       <c r="A237" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B237" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C237">
         <v>47.24402</v>
@@ -12565,10 +12572,10 @@
     </row>
     <row r="238" spans="1:30">
       <c r="A238" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B238" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C238">
         <v>47.182296</v>
@@ -12621,10 +12628,10 @@
     </row>
     <row r="239" spans="1:30">
       <c r="A239" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B239" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C239">
         <v>47.561781</v>
@@ -12677,10 +12684,10 @@
     </row>
     <row r="240" spans="1:30">
       <c r="A240" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B240" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C240">
         <v>47.561781</v>
@@ -12733,10 +12740,10 @@
     </row>
     <row r="241" spans="1:30">
       <c r="A241" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B241" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C241">
         <v>47.561781</v>
@@ -12792,10 +12799,10 @@
     </row>
     <row r="242" spans="1:30">
       <c r="A242" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B242" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C242">
         <v>47.561781</v>
@@ -12848,10 +12855,10 @@
     </row>
     <row r="243" spans="1:30">
       <c r="A243" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B243" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C243">
         <v>47.561781</v>
@@ -12904,10 +12911,10 @@
     </row>
     <row r="244" spans="1:30">
       <c r="A244" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B244" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C244">
         <v>47.561781</v>
@@ -12960,10 +12967,10 @@
     </row>
     <row r="245" spans="1:30">
       <c r="A245" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B245" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C245">
         <v>47.418972</v>
@@ -13022,10 +13029,10 @@
     </row>
     <row r="246" spans="1:30">
       <c r="A246" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B246" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C246">
         <v>45.99768066</v>
@@ -13045,10 +13052,10 @@
     </row>
     <row r="247" spans="1:30">
       <c r="A247" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B247" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C247">
         <v>45.46832275</v>
@@ -13068,10 +13075,10 @@
     </row>
     <row r="248" spans="1:30">
       <c r="A248" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B248" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C248">
         <v>45.24450684</v>
@@ -13091,10 +13098,10 @@
     </row>
     <row r="249" spans="1:30">
       <c r="A249" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B249" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C249">
         <v>44.97888184</v>
@@ -13114,10 +13121,10 @@
     </row>
     <row r="250" spans="1:30">
       <c r="A250" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B250" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C250">
         <v>44.90747070000001</v>
@@ -13137,10 +13144,10 @@
     </row>
     <row r="251" spans="1:30">
       <c r="A251" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B251" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C251">
         <v>44.64111328</v>
@@ -13160,10 +13167,10 @@
     </row>
     <row r="252" spans="1:30">
       <c r="A252" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B252" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C252">
         <v>44.52209473</v>
@@ -13183,10 +13190,10 @@
     </row>
     <row r="253" spans="1:30">
       <c r="A253" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B253" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C253">
         <v>44.43450928</v>
@@ -13206,10 +13213,10 @@
     </row>
     <row r="254" spans="1:30">
       <c r="A254" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B254" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C254">
         <v>43.9876709</v>
@@ -13229,10 +13236,10 @@
     </row>
     <row r="255" spans="1:30">
       <c r="A255" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B255" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C255">
         <v>43.70910645</v>
@@ -13252,10 +13259,10 @@
     </row>
     <row r="256" spans="1:30">
       <c r="A256" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B256" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C256">
         <v>45.89658</v>
@@ -13311,10 +13318,10 @@
     </row>
     <row r="257" spans="1:30">
       <c r="A257" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B257" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C257">
         <v>45.89658</v>
@@ -13367,10 +13374,10 @@
     </row>
     <row r="258" spans="1:30">
       <c r="A258" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B258" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C258">
         <v>45.89658</v>
@@ -13420,7 +13427,7 @@
     </row>
     <row r="259" spans="1:30">
       <c r="A259" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C259">
         <v>45.8966667</v>
@@ -13470,10 +13477,10 @@
     </row>
     <row r="260" spans="1:30">
       <c r="A260" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B260" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C260">
         <v>43.52673060000001</v>
@@ -13493,10 +13500,10 @@
     </row>
     <row r="261" spans="1:30">
       <c r="A261" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B261" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C261">
         <v>43.52673060000001</v>
@@ -13516,10 +13523,10 @@
     </row>
     <row r="262" spans="1:30">
       <c r="A262" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B262" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C262">
         <v>45.383419</v>
@@ -13569,10 +13576,10 @@
     </row>
     <row r="263" spans="1:30">
       <c r="A263" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B263" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C263">
         <v>46.39416705</v>
@@ -13622,10 +13629,10 @@
     </row>
     <row r="264" spans="1:30">
       <c r="A264" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B264" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C264">
         <v>46.39416705</v>
@@ -13660,10 +13667,10 @@
     </row>
     <row r="265" spans="1:30">
       <c r="A265" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B265" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C265">
         <v>44.05085725</v>
@@ -13704,10 +13711,10 @@
     </row>
     <row r="266" spans="1:30">
       <c r="A266" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B266" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C266">
         <v>44.050857</v>
@@ -13748,10 +13755,10 @@
     </row>
     <row r="267" spans="1:30">
       <c r="A267" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B267" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C267">
         <v>45.45126276</v>
@@ -13771,10 +13778,10 @@
     </row>
     <row r="268" spans="1:30">
       <c r="A268" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B268" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C268">
         <v>45.45094967</v>
@@ -13827,10 +13834,10 @@
     </row>
     <row r="269" spans="1:30">
       <c r="A269" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B269" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C269">
         <v>45.55049926</v>
@@ -13880,10 +13887,10 @@
     </row>
     <row r="270" spans="1:30">
       <c r="A270" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B270" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C270">
         <v>45.92770512</v>
@@ -13903,10 +13910,10 @@
     </row>
     <row r="271" spans="1:30">
       <c r="A271" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B271" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C271">
         <v>44.82633807</v>
@@ -13935,10 +13942,10 @@
     </row>
     <row r="272" spans="1:30">
       <c r="A272" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B272" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C272">
         <v>44.82501521</v>
@@ -13991,7 +13998,7 @@
     </row>
     <row r="273" spans="1:30">
       <c r="A273" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C273">
         <v>44.08313673</v>
@@ -14011,7 +14018,7 @@
     </row>
     <row r="274" spans="1:30">
       <c r="A274" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C274">
         <v>45.89602574</v>
@@ -14055,10 +14062,10 @@
     </row>
     <row r="275" spans="1:30">
       <c r="A275" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B275" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C275">
         <v>45.27989606</v>
@@ -14099,10 +14106,10 @@
     </row>
     <row r="276" spans="1:30">
       <c r="A276" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B276" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C276">
         <v>45.51328189</v>
@@ -14125,10 +14132,10 @@
     </row>
     <row r="277" spans="1:30">
       <c r="A277" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B277" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C277">
         <v>45.51346483</v>
@@ -14181,10 +14188,10 @@
     </row>
     <row r="278" spans="1:30">
       <c r="A278" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B278" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C278">
         <v>45.5133183</v>
@@ -14237,10 +14244,10 @@
     </row>
     <row r="279" spans="1:30">
       <c r="A279" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B279" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C279">
         <v>45.51326532</v>
@@ -14290,10 +14297,10 @@
     </row>
     <row r="280" spans="1:30">
       <c r="A280" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B280" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C280">
         <v>45.51325115</v>
@@ -14346,10 +14353,10 @@
     </row>
     <row r="281" spans="1:30">
       <c r="A281" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B281" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C281">
         <v>44.1746806</v>
@@ -14408,10 +14415,10 @@
     </row>
     <row r="282" spans="1:30">
       <c r="A282" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B282" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C282">
         <v>44.16989906</v>
@@ -14467,10 +14474,10 @@
     </row>
     <row r="283" spans="1:30">
       <c r="A283" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B283" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C283">
         <v>44.1748639</v>
@@ -14526,7 +14533,7 @@
     </row>
     <row r="284" spans="1:30">
       <c r="A284" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C284">
         <v>44.95259221</v>
@@ -14546,10 +14553,10 @@
     </row>
     <row r="285" spans="1:30">
       <c r="A285" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B285" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C285">
         <v>44.91308334</v>
@@ -14572,10 +14579,10 @@
     </row>
     <row r="286" spans="1:30">
       <c r="A286" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B286" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C286">
         <v>44.137049</v>
@@ -14595,10 +14602,10 @@
     </row>
     <row r="287" spans="1:30">
       <c r="A287" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B287" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C287">
         <v>45.47125836</v>
@@ -14648,10 +14655,10 @@
     </row>
     <row r="288" spans="1:30">
       <c r="A288" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B288" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C288">
         <v>45.4712901</v>
@@ -14701,10 +14708,10 @@
     </row>
     <row r="289" spans="1:30">
       <c r="A289" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B289" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C289">
         <v>45.46584195</v>
@@ -14724,10 +14731,10 @@
     </row>
     <row r="290" spans="1:30">
       <c r="A290" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B290" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C290">
         <v>45.14215687</v>
@@ -14783,10 +14790,10 @@
     </row>
     <row r="291" spans="1:30">
       <c r="A291" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B291" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C291">
         <v>45.895295</v>
@@ -14830,10 +14837,10 @@
     </row>
     <row r="292" spans="1:30">
       <c r="A292" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B292" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C292">
         <v>46.1592</v>
@@ -14874,7 +14881,7 @@
     </row>
     <row r="293" spans="1:30">
       <c r="A293" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C293">
         <v>46.3392</v>
@@ -14918,7 +14925,7 @@
     </row>
     <row r="294" spans="1:30">
       <c r="A294" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C294">
         <v>46.27117</v>
@@ -14959,7 +14966,7 @@
     </row>
     <row r="295" spans="1:30">
       <c r="A295" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C295">
         <v>46.307762</v>
@@ -15006,7 +15013,7 @@
     </row>
     <row r="296" spans="1:30">
       <c r="A296" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C296">
         <v>46.4044</v>
@@ -15053,7 +15060,7 @@
     </row>
     <row r="297" spans="1:30">
       <c r="A297" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C297">
         <v>46.3303</v>
@@ -15109,7 +15116,7 @@
     </row>
     <row r="298" spans="1:30">
       <c r="A298" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C298">
         <v>46.3049</v>
@@ -15162,7 +15169,7 @@
     </row>
     <row r="299" spans="1:30">
       <c r="A299" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C299">
         <v>46.3547</v>
@@ -15218,7 +15225,7 @@
     </row>
     <row r="300" spans="1:30">
       <c r="A300" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C300">
         <v>46.1553</v>
@@ -15259,7 +15266,7 @@
     </row>
     <row r="301" spans="1:30">
       <c r="A301" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C301">
         <v>46.1567</v>
@@ -15303,7 +15310,7 @@
     </row>
     <row r="302" spans="1:30">
       <c r="A302" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C302">
         <v>46.13</v>
@@ -15350,7 +15357,7 @@
     </row>
     <row r="303" spans="1:30">
       <c r="A303" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C303">
         <v>46.4391</v>
@@ -15391,7 +15398,7 @@
     </row>
     <row r="304" spans="1:30">
       <c r="A304" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C304">
         <v>46.4027</v>
@@ -15432,7 +15439,7 @@
     </row>
     <row r="305" spans="1:30">
       <c r="A305" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C305">
         <v>46.3861</v>
@@ -15473,7 +15480,7 @@
     </row>
     <row r="306" spans="1:30">
       <c r="A306" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C306">
         <v>46.4024</v>
@@ -15514,7 +15521,7 @@
     </row>
     <row r="307" spans="1:30">
       <c r="A307" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C307">
         <v>46.4065</v>
@@ -15555,7 +15562,7 @@
     </row>
     <row r="308" spans="1:30">
       <c r="A308" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C308">
         <v>46.4235</v>
@@ -15593,7 +15600,7 @@
     </row>
     <row r="309" spans="1:30">
       <c r="A309" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C309">
         <v>46.4193</v>
@@ -15634,7 +15641,7 @@
     </row>
     <row r="310" spans="1:30">
       <c r="A310" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C310">
         <v>46.3962</v>
@@ -15675,7 +15682,7 @@
     </row>
     <row r="311" spans="1:30">
       <c r="A311" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C311">
         <v>46.3114</v>
@@ -15716,10 +15723,10 @@
     </row>
     <row r="312" spans="1:30">
       <c r="A312" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B312" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C312">
         <v>47.75909424</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/before_conversion_alps_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/before_conversion_alps_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="460">
   <si>
     <t>location</t>
   </si>
@@ -1370,6 +1370,30 @@
   </si>
   <si>
     <t>Tüfferbad</t>
+  </si>
+  <si>
+    <t>Sand and Gravel</t>
+  </si>
+  <si>
+    <t>Gypsum</t>
+  </si>
+  <si>
+    <t>Rhyolite</t>
+  </si>
+  <si>
+    <t>Andesite</t>
+  </si>
+  <si>
+    <t>Basalt</t>
+  </si>
+  <si>
+    <t>Syenite</t>
+  </si>
+  <si>
+    <t>Breccia</t>
+  </si>
+  <si>
+    <t>Limestone</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1764,7 @@
     <col min="2" max="2" width="48.7109375" customWidth="1"/>
     <col min="3" max="4" width="19.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
@@ -1872,8 +1896,8 @@
       <c r="D2">
         <v>11.77885556</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="F2" t="s">
+        <v>452</v>
       </c>
       <c r="H2">
         <v>48.9</v>
@@ -1895,8 +1919,8 @@
       <c r="D3">
         <v>11.64996667</v>
       </c>
-      <c r="F3">
-        <v>6</v>
+      <c r="F3" t="s">
+        <v>453</v>
       </c>
       <c r="H3">
         <v>34.6</v>
@@ -1918,8 +1942,8 @@
       <c r="D4">
         <v>11.6483</v>
       </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="F4" t="s">
+        <v>452</v>
       </c>
       <c r="H4">
         <v>30.3</v>
@@ -1941,8 +1965,8 @@
       <c r="D5">
         <v>11.64552222</v>
       </c>
-      <c r="F5">
-        <v>7</v>
+      <c r="F5" t="s">
+        <v>454</v>
       </c>
       <c r="H5">
         <v>21.2</v>
@@ -1964,8 +1988,8 @@
       <c r="D6">
         <v>8.45300523</v>
       </c>
-      <c r="F6">
-        <v>6</v>
+      <c r="F6" t="s">
+        <v>453</v>
       </c>
       <c r="H6">
         <v>59</v>
@@ -1987,8 +2011,8 @@
       <c r="D7">
         <v>10.359474</v>
       </c>
-      <c r="F7">
-        <v>1</v>
+      <c r="F7" t="s">
+        <v>452</v>
       </c>
       <c r="H7">
         <v>37.5</v>
@@ -2031,8 +2055,8 @@
       <c r="D8">
         <v>10.35926</v>
       </c>
-      <c r="F8">
-        <v>1</v>
+      <c r="F8" t="s">
+        <v>452</v>
       </c>
       <c r="H8">
         <v>36.5</v>
@@ -2054,8 +2078,8 @@
       <c r="D9">
         <v>10.35956</v>
       </c>
-      <c r="F9">
-        <v>1</v>
+      <c r="F9" t="s">
+        <v>452</v>
       </c>
       <c r="H9">
         <v>41</v>
@@ -2098,8 +2122,8 @@
       <c r="D10">
         <v>10.358343</v>
       </c>
-      <c r="F10">
-        <v>1</v>
+      <c r="F10" t="s">
+        <v>452</v>
       </c>
       <c r="H10">
         <v>42</v>
@@ -2142,8 +2166,8 @@
       <c r="D11">
         <v>10.357372</v>
       </c>
-      <c r="F11">
-        <v>1</v>
+      <c r="F11" t="s">
+        <v>452</v>
       </c>
       <c r="H11">
         <v>36</v>
@@ -2165,8 +2189,8 @@
       <c r="D12">
         <v>10.357291</v>
       </c>
-      <c r="F12">
-        <v>1</v>
+      <c r="F12" t="s">
+        <v>452</v>
       </c>
       <c r="H12">
         <v>34.5</v>
@@ -2188,8 +2212,8 @@
       <c r="D13">
         <v>10.3643</v>
       </c>
-      <c r="F13">
-        <v>1</v>
+      <c r="F13" t="s">
+        <v>452</v>
       </c>
       <c r="H13">
         <v>18.5</v>
@@ -2211,8 +2235,8 @@
       <c r="D14">
         <v>10.359989</v>
       </c>
-      <c r="F14">
-        <v>1</v>
+      <c r="F14" t="s">
+        <v>452</v>
       </c>
       <c r="H14">
         <v>37</v>
@@ -2255,8 +2279,8 @@
       <c r="D15">
         <v>10.36117</v>
       </c>
-      <c r="F15">
-        <v>1</v>
+      <c r="F15" t="s">
+        <v>452</v>
       </c>
       <c r="H15">
         <v>18.5</v>
@@ -2299,8 +2323,8 @@
       <c r="D16">
         <v>10.360826</v>
       </c>
-      <c r="F16">
-        <v>1</v>
+      <c r="F16" t="s">
+        <v>452</v>
       </c>
       <c r="H16">
         <v>39.5</v>
@@ -2343,8 +2367,8 @@
       <c r="D17">
         <v>10.8863889</v>
       </c>
-      <c r="F17">
-        <v>6</v>
+      <c r="F17" t="s">
+        <v>453</v>
       </c>
       <c r="H17">
         <v>27</v>
@@ -2366,8 +2390,8 @@
       <c r="D18">
         <v>6.9867</v>
       </c>
-      <c r="F18">
-        <v>8</v>
+      <c r="F18" t="s">
+        <v>455</v>
       </c>
       <c r="H18">
         <v>26.5</v>
@@ -2392,8 +2416,8 @@
       <c r="D19">
         <v>8.519166667</v>
       </c>
-      <c r="F19">
-        <v>8</v>
+      <c r="F19" t="s">
+        <v>455</v>
       </c>
       <c r="H19">
         <v>27.2</v>
@@ -2415,8 +2439,8 @@
       <c r="D20">
         <v>8.541600000000001</v>
       </c>
-      <c r="F20">
-        <v>8</v>
+      <c r="F20" t="s">
+        <v>455</v>
       </c>
       <c r="H20">
         <v>25.7</v>
@@ -2471,8 +2495,8 @@
       <c r="D21">
         <v>12.02082</v>
       </c>
-      <c r="F21">
-        <v>6</v>
+      <c r="F21" t="s">
+        <v>453</v>
       </c>
       <c r="H21">
         <v>7.9</v>
@@ -2494,8 +2518,8 @@
       <c r="D22">
         <v>11.8852</v>
       </c>
-      <c r="F22">
-        <v>6</v>
+      <c r="F22" t="s">
+        <v>453</v>
       </c>
       <c r="H22">
         <v>6.4</v>
@@ -2517,8 +2541,8 @@
       <c r="D23">
         <v>12.15402</v>
       </c>
-      <c r="F23">
-        <v>6</v>
+      <c r="F23" t="s">
+        <v>453</v>
       </c>
       <c r="H23">
         <v>5.2</v>
@@ -2540,8 +2564,8 @@
       <c r="D24">
         <v>12.25903</v>
       </c>
-      <c r="F24">
-        <v>6</v>
+      <c r="F24" t="s">
+        <v>453</v>
       </c>
       <c r="H24">
         <v>7.4</v>
@@ -2563,8 +2587,8 @@
       <c r="D25">
         <v>12.21316</v>
       </c>
-      <c r="F25">
-        <v>6</v>
+      <c r="F25" t="s">
+        <v>453</v>
       </c>
       <c r="H25">
         <v>5.8</v>
@@ -2586,8 +2610,8 @@
       <c r="D26">
         <v>12.21544</v>
       </c>
-      <c r="F26">
-        <v>6</v>
+      <c r="F26" t="s">
+        <v>453</v>
       </c>
       <c r="H26">
         <v>8</v>
@@ -2609,8 +2633,8 @@
       <c r="D27">
         <v>11.9727</v>
       </c>
-      <c r="F27">
-        <v>8</v>
+      <c r="F27" t="s">
+        <v>455</v>
       </c>
       <c r="H27">
         <v>6.2</v>
@@ -2632,8 +2656,8 @@
       <c r="D28">
         <v>12.1707</v>
       </c>
-      <c r="F28">
-        <v>6</v>
+      <c r="F28" t="s">
+        <v>453</v>
       </c>
       <c r="H28">
         <v>5.5</v>
@@ -2655,8 +2679,8 @@
       <c r="D29">
         <v>12.15361</v>
       </c>
-      <c r="F29">
-        <v>6</v>
+      <c r="F29" t="s">
+        <v>453</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -2678,8 +2702,8 @@
       <c r="D30">
         <v>12.15865</v>
       </c>
-      <c r="F30">
-        <v>6</v>
+      <c r="F30" t="s">
+        <v>453</v>
       </c>
       <c r="H30">
         <v>5.8</v>
@@ -2701,8 +2725,8 @@
       <c r="D31">
         <v>11.96932</v>
       </c>
-      <c r="F31">
-        <v>8</v>
+      <c r="F31" t="s">
+        <v>455</v>
       </c>
       <c r="H31">
         <v>8.199999999999999</v>
@@ -2724,8 +2748,8 @@
       <c r="D32">
         <v>9.725339999999999</v>
       </c>
-      <c r="F32">
-        <v>9</v>
+      <c r="F32" t="s">
+        <v>456</v>
       </c>
       <c r="H32">
         <v>37.9</v>
@@ -2777,8 +2801,8 @@
       <c r="D33">
         <v>6.9689</v>
       </c>
-      <c r="F33">
-        <v>8</v>
+      <c r="F33" t="s">
+        <v>455</v>
       </c>
       <c r="H33">
         <v>22.3</v>
@@ -2833,8 +2857,8 @@
       <c r="D34">
         <v>9.662777778000001</v>
       </c>
-      <c r="F34">
-        <v>6</v>
+      <c r="F34" t="s">
+        <v>453</v>
       </c>
       <c r="H34">
         <v>27</v>
@@ -2856,8 +2880,8 @@
       <c r="D35">
         <v>9.662777778000001</v>
       </c>
-      <c r="F35">
-        <v>6</v>
+      <c r="F35" t="s">
+        <v>453</v>
       </c>
       <c r="H35">
         <v>21.7</v>
@@ -2879,8 +2903,8 @@
       <c r="D36">
         <v>9.662777778000001</v>
       </c>
-      <c r="F36">
-        <v>6</v>
+      <c r="F36" t="s">
+        <v>453</v>
       </c>
       <c r="H36">
         <v>18.5</v>
@@ -2905,8 +2929,8 @@
       <c r="E37">
         <v>1650</v>
       </c>
-      <c r="F37">
-        <v>8</v>
+      <c r="F37" t="s">
+        <v>455</v>
       </c>
       <c r="H37">
         <v>29.2</v>
@@ -2958,8 +2982,8 @@
       <c r="E38">
         <v>1650</v>
       </c>
-      <c r="F38">
-        <v>8</v>
+      <c r="F38" t="s">
+        <v>455</v>
       </c>
       <c r="H38">
         <v>38.6</v>
@@ -3011,8 +3035,8 @@
       <c r="D39">
         <v>10.609565</v>
       </c>
-      <c r="F39">
-        <v>11</v>
+      <c r="F39" t="s">
+        <v>457</v>
       </c>
       <c r="H39">
         <v>69.90000000000001</v>
@@ -3034,8 +3058,8 @@
       <c r="D40">
         <v>7.269966667</v>
       </c>
-      <c r="F40">
-        <v>8</v>
+      <c r="F40" t="s">
+        <v>455</v>
       </c>
       <c r="H40">
         <v>63</v>
@@ -3087,8 +3111,8 @@
       <c r="D41">
         <v>7.269966667</v>
       </c>
-      <c r="F41">
-        <v>8</v>
+      <c r="F41" t="s">
+        <v>455</v>
       </c>
       <c r="H41">
         <v>46.8</v>
@@ -3110,8 +3134,8 @@
       <c r="D42">
         <v>7.269966667</v>
       </c>
-      <c r="F42">
-        <v>8</v>
+      <c r="F42" t="s">
+        <v>455</v>
       </c>
       <c r="H42">
         <v>60.4</v>
@@ -3133,8 +3157,8 @@
       <c r="D43">
         <v>7.269966667</v>
       </c>
-      <c r="F43">
-        <v>8</v>
+      <c r="F43" t="s">
+        <v>455</v>
       </c>
       <c r="H43">
         <v>55.4</v>
@@ -3186,8 +3210,8 @@
       <c r="D44">
         <v>7.268888888999999</v>
       </c>
-      <c r="F44">
-        <v>8</v>
+      <c r="F44" t="s">
+        <v>455</v>
       </c>
       <c r="H44">
         <v>48.8</v>
@@ -3233,8 +3257,8 @@
       <c r="D45">
         <v>7.077744444</v>
       </c>
-      <c r="F45">
-        <v>8</v>
+      <c r="F45" t="s">
+        <v>455</v>
       </c>
       <c r="H45">
         <v>46.7</v>
@@ -3286,8 +3310,8 @@
       <c r="D46">
         <v>7.076666667</v>
       </c>
-      <c r="F46">
-        <v>8</v>
+      <c r="F46" t="s">
+        <v>455</v>
       </c>
       <c r="H46">
         <v>49.5</v>
@@ -3309,8 +3333,8 @@
       <c r="D47">
         <v>7.077744444</v>
       </c>
-      <c r="F47">
-        <v>8</v>
+      <c r="F47" t="s">
+        <v>455</v>
       </c>
       <c r="H47">
         <v>50.5</v>
@@ -3356,8 +3380,8 @@
       <c r="D48">
         <v>7.077744444</v>
       </c>
-      <c r="F48">
-        <v>8</v>
+      <c r="F48" t="s">
+        <v>455</v>
       </c>
       <c r="H48">
         <v>55.2</v>
@@ -3409,8 +3433,8 @@
       <c r="D49">
         <v>7.077744444</v>
       </c>
-      <c r="F49">
-        <v>8</v>
+      <c r="F49" t="s">
+        <v>455</v>
       </c>
       <c r="H49">
         <v>55.6</v>
@@ -3462,8 +3486,8 @@
       <c r="D50">
         <v>7.077744444</v>
       </c>
-      <c r="F50">
-        <v>8</v>
+      <c r="F50" t="s">
+        <v>455</v>
       </c>
       <c r="H50">
         <v>61.2</v>
@@ -3485,8 +3509,8 @@
       <c r="D51">
         <v>7.077744444</v>
       </c>
-      <c r="F51">
-        <v>8</v>
+      <c r="F51" t="s">
+        <v>455</v>
       </c>
       <c r="H51">
         <v>58</v>
@@ -3508,8 +3532,8 @@
       <c r="D52">
         <v>8.4733</v>
       </c>
-      <c r="F52">
-        <v>6</v>
+      <c r="F52" t="s">
+        <v>453</v>
       </c>
       <c r="H52">
         <v>38.2</v>
@@ -3531,8 +3555,8 @@
       <c r="D53">
         <v>8.480555556000001</v>
       </c>
-      <c r="F53">
-        <v>1</v>
+      <c r="F53" t="s">
+        <v>452</v>
       </c>
       <c r="H53">
         <v>70.5</v>
@@ -3578,8 +3602,8 @@
       <c r="D54">
         <v>8.4733</v>
       </c>
-      <c r="F54">
-        <v>6</v>
+      <c r="F54" t="s">
+        <v>453</v>
       </c>
       <c r="H54">
         <v>56</v>
@@ -3601,8 +3625,8 @@
       <c r="D55">
         <v>8.466666667</v>
       </c>
-      <c r="F55">
-        <v>6</v>
+      <c r="F55" t="s">
+        <v>453</v>
       </c>
       <c r="H55">
         <v>69.5</v>
@@ -3654,8 +3678,8 @@
       <c r="D56">
         <v>8.466666667</v>
       </c>
-      <c r="F56">
-        <v>6</v>
+      <c r="F56" t="s">
+        <v>453</v>
       </c>
       <c r="H56">
         <v>17.4</v>
@@ -3707,8 +3731,8 @@
       <c r="D57">
         <v>8.466666667</v>
       </c>
-      <c r="F57">
-        <v>6</v>
+      <c r="F57" t="s">
+        <v>453</v>
       </c>
       <c r="H57">
         <v>18.7</v>
@@ -3760,8 +3784,8 @@
       <c r="D58">
         <v>8.483333332999999</v>
       </c>
-      <c r="F58">
-        <v>6</v>
+      <c r="F58" t="s">
+        <v>453</v>
       </c>
       <c r="H58">
         <v>30.1</v>
@@ -3813,8 +3837,8 @@
       <c r="D59">
         <v>8.449999999999999</v>
       </c>
-      <c r="F59">
-        <v>6</v>
+      <c r="F59" t="s">
+        <v>453</v>
       </c>
       <c r="H59">
         <v>13.7</v>
@@ -3866,8 +3890,8 @@
       <c r="D60">
         <v>8.5</v>
       </c>
-      <c r="F60">
-        <v>1</v>
+      <c r="F60" t="s">
+        <v>452</v>
       </c>
       <c r="H60">
         <v>37.9</v>
@@ -3919,8 +3943,8 @@
       <c r="D61">
         <v>8.5</v>
       </c>
-      <c r="F61">
-        <v>1</v>
+      <c r="F61" t="s">
+        <v>452</v>
       </c>
       <c r="H61">
         <v>32</v>
@@ -3972,8 +3996,8 @@
       <c r="D62">
         <v>8.5</v>
       </c>
-      <c r="F62">
-        <v>1</v>
+      <c r="F62" t="s">
+        <v>452</v>
       </c>
       <c r="H62">
         <v>23</v>
@@ -4025,8 +4049,8 @@
       <c r="D63">
         <v>8.445277777999999</v>
       </c>
-      <c r="F63">
-        <v>4</v>
+      <c r="F63" t="s">
+        <v>458</v>
       </c>
       <c r="H63">
         <v>14.5</v>
@@ -4075,8 +4099,8 @@
       <c r="D64">
         <v>8.466666667</v>
       </c>
-      <c r="F64">
-        <v>6</v>
+      <c r="F64" t="s">
+        <v>453</v>
       </c>
       <c r="H64">
         <v>69.5</v>
@@ -4128,8 +4152,8 @@
       <c r="D65">
         <v>8.5</v>
       </c>
-      <c r="F65">
-        <v>1</v>
+      <c r="F65" t="s">
+        <v>452</v>
       </c>
       <c r="H65">
         <v>31.5</v>
@@ -4181,8 +4205,8 @@
       <c r="D66">
         <v>10.886389</v>
       </c>
-      <c r="F66">
-        <v>6</v>
+      <c r="F66" t="s">
+        <v>453</v>
       </c>
       <c r="H66">
         <v>27</v>
@@ -4204,8 +4228,8 @@
       <c r="D67">
         <v>8.654688900000002</v>
       </c>
-      <c r="F67">
-        <v>1</v>
+      <c r="F67" t="s">
+        <v>452</v>
       </c>
       <c r="H67">
         <v>22.5</v>
@@ -4227,8 +4251,8 @@
       <c r="D68">
         <v>11.607467</v>
       </c>
-      <c r="F68">
-        <v>1</v>
+      <c r="F68" t="s">
+        <v>452</v>
       </c>
       <c r="H68">
         <v>24</v>
@@ -4250,8 +4274,8 @@
       <c r="D69">
         <v>11.742467</v>
       </c>
-      <c r="F69">
-        <v>1</v>
+      <c r="F69" t="s">
+        <v>452</v>
       </c>
       <c r="H69">
         <v>28.3</v>
@@ -4273,8 +4297,8 @@
       <c r="D70">
         <v>11.744411</v>
       </c>
-      <c r="F70">
-        <v>1</v>
+      <c r="F70" t="s">
+        <v>452</v>
       </c>
       <c r="H70">
         <v>43.1</v>
@@ -4296,8 +4320,8 @@
       <c r="D71">
         <v>11.645244</v>
       </c>
-      <c r="F71">
-        <v>1</v>
+      <c r="F71" t="s">
+        <v>452</v>
       </c>
       <c r="H71">
         <v>36</v>
@@ -4319,8 +4343,8 @@
       <c r="D72">
         <v>11.556356</v>
       </c>
-      <c r="F72">
-        <v>1</v>
+      <c r="F72" t="s">
+        <v>452</v>
       </c>
       <c r="H72">
         <v>28.5</v>
@@ -4345,8 +4369,8 @@
       <c r="E73">
         <v>54</v>
       </c>
-      <c r="F73">
-        <v>6</v>
+      <c r="F73" t="s">
+        <v>453</v>
       </c>
       <c r="H73">
         <v>26.5</v>
@@ -4368,8 +4392,8 @@
       <c r="D74">
         <v>11.569967</v>
       </c>
-      <c r="F74">
-        <v>1</v>
+      <c r="F74" t="s">
+        <v>452</v>
       </c>
       <c r="H74">
         <v>25.2</v>
@@ -4391,8 +4415,8 @@
       <c r="D75">
         <v>11.596633</v>
       </c>
-      <c r="F75">
-        <v>1</v>
+      <c r="F75" t="s">
+        <v>452</v>
       </c>
       <c r="H75">
         <v>24.6</v>
@@ -4414,8 +4438,8 @@
       <c r="D76">
         <v>11.194967</v>
       </c>
-      <c r="F76">
-        <v>1</v>
+      <c r="F76" t="s">
+        <v>452</v>
       </c>
       <c r="H76">
         <v>26.9</v>
@@ -4440,8 +4464,8 @@
       <c r="E77">
         <v>100</v>
       </c>
-      <c r="F77">
-        <v>1</v>
+      <c r="F77" t="s">
+        <v>452</v>
       </c>
       <c r="H77">
         <v>26.4</v>
@@ -4463,8 +4487,8 @@
       <c r="D78">
         <v>11.758889</v>
       </c>
-      <c r="F78">
-        <v>7</v>
+      <c r="F78" t="s">
+        <v>454</v>
       </c>
       <c r="H78">
         <v>49</v>
@@ -4486,8 +4510,8 @@
       <c r="D79">
         <v>11.748889</v>
       </c>
-      <c r="F79">
-        <v>1</v>
+      <c r="F79" t="s">
+        <v>452</v>
       </c>
       <c r="H79">
         <v>32.2</v>
@@ -4509,8 +4533,8 @@
       <c r="D80">
         <v>11.586389</v>
       </c>
-      <c r="F80">
-        <v>1</v>
+      <c r="F80" t="s">
+        <v>452</v>
       </c>
       <c r="H80">
         <v>25.8</v>
@@ -4532,8 +4556,8 @@
       <c r="D81">
         <v>11.556944</v>
       </c>
-      <c r="F81">
-        <v>1</v>
+      <c r="F81" t="s">
+        <v>452</v>
       </c>
       <c r="H81">
         <v>28.8</v>
@@ -4552,8 +4576,8 @@
       <c r="D82">
         <v>7.827468</v>
       </c>
-      <c r="F82">
-        <v>8</v>
+      <c r="F82" t="s">
+        <v>455</v>
       </c>
       <c r="H82">
         <v>42</v>
@@ -4599,8 +4623,8 @@
       <c r="D83">
         <v>8.94303</v>
       </c>
-      <c r="F83">
-        <v>1</v>
+      <c r="F83" t="s">
+        <v>452</v>
       </c>
       <c r="H83">
         <v>24.9</v>
@@ -4652,8 +4676,8 @@
       <c r="D84">
         <v>8.94303</v>
       </c>
-      <c r="F84">
-        <v>1</v>
+      <c r="F84" t="s">
+        <v>452</v>
       </c>
       <c r="H84">
         <v>24.5</v>
@@ -4702,8 +4726,8 @@
       <c r="D85">
         <v>8.94303</v>
       </c>
-      <c r="F85">
-        <v>1</v>
+      <c r="F85" t="s">
+        <v>452</v>
       </c>
       <c r="H85">
         <v>24.2</v>
@@ -4752,8 +4776,8 @@
       <c r="D86">
         <v>9.44491</v>
       </c>
-      <c r="F86">
-        <v>6</v>
+      <c r="F86" t="s">
+        <v>453</v>
       </c>
       <c r="H86">
         <v>18</v>
@@ -4805,8 +4829,8 @@
       <c r="D87">
         <v>9.48696</v>
       </c>
-      <c r="F87">
-        <v>5</v>
+      <c r="F87" t="s">
+        <v>459</v>
       </c>
       <c r="H87">
         <v>36.5</v>
@@ -4858,8 +4882,8 @@
       <c r="D88">
         <v>9.65865</v>
       </c>
-      <c r="F88">
-        <v>6</v>
+      <c r="F88" t="s">
+        <v>453</v>
       </c>
       <c r="H88">
         <v>17</v>
@@ -4899,8 +4923,8 @@
       <c r="D89">
         <v>7.098660000000002</v>
       </c>
-      <c r="F89">
-        <v>9</v>
+      <c r="F89" t="s">
+        <v>456</v>
       </c>
       <c r="H89">
         <v>21.1</v>
@@ -4955,8 +4979,8 @@
       <c r="D90">
         <v>7.92536</v>
       </c>
-      <c r="F90">
-        <v>8</v>
+      <c r="F90" t="s">
+        <v>455</v>
       </c>
       <c r="H90">
         <v>16.1</v>
@@ -5011,8 +5035,8 @@
       <c r="D91">
         <v>7.92939</v>
       </c>
-      <c r="F91">
-        <v>8</v>
+      <c r="F91" t="s">
+        <v>455</v>
       </c>
       <c r="H91">
         <v>22.5</v>
@@ -5067,8 +5091,8 @@
       <c r="D92">
         <v>7.41623</v>
       </c>
-      <c r="F92">
-        <v>3</v>
+      <c r="F92" t="s">
+        <v>454</v>
       </c>
       <c r="H92">
         <v>28</v>
@@ -5123,8 +5147,8 @@
       <c r="D93">
         <v>7.41597</v>
       </c>
-      <c r="F93">
-        <v>3</v>
+      <c r="F93" t="s">
+        <v>454</v>
       </c>
       <c r="H93">
         <v>24.9</v>
@@ -5179,8 +5203,8 @@
       <c r="D94">
         <v>8.36098</v>
       </c>
-      <c r="F94">
-        <v>8</v>
+      <c r="F94" t="s">
+        <v>455</v>
       </c>
       <c r="H94">
         <v>18.6</v>
@@ -5232,8 +5256,8 @@
       <c r="D95">
         <v>7.011839999999999</v>
       </c>
-      <c r="F95">
-        <v>1</v>
+      <c r="F95" t="s">
+        <v>452</v>
       </c>
       <c r="H95">
         <v>55</v>
@@ -5279,8 +5303,8 @@
       <c r="D96">
         <v>7.64338</v>
       </c>
-      <c r="F96">
-        <v>6</v>
+      <c r="F96" t="s">
+        <v>453</v>
       </c>
       <c r="H96">
         <v>45.5</v>
@@ -5335,8 +5359,8 @@
       <c r="D97">
         <v>7.632639999999999</v>
       </c>
-      <c r="F97">
-        <v>1</v>
+      <c r="F97" t="s">
+        <v>452</v>
       </c>
       <c r="H97">
         <v>45.9</v>
@@ -5391,8 +5415,8 @@
       <c r="D98">
         <v>7.63134</v>
       </c>
-      <c r="F98">
-        <v>1</v>
+      <c r="F98" t="s">
+        <v>452</v>
       </c>
       <c r="H98">
         <v>37.3</v>
@@ -5447,8 +5471,8 @@
       <c r="D99">
         <v>7.6346</v>
       </c>
-      <c r="F99">
-        <v>1</v>
+      <c r="F99" t="s">
+        <v>452</v>
       </c>
       <c r="H99">
         <v>43.6</v>
@@ -5503,8 +5527,8 @@
       <c r="D100">
         <v>7.62547</v>
       </c>
-      <c r="F100">
-        <v>1</v>
+      <c r="F100" t="s">
+        <v>452</v>
       </c>
       <c r="H100">
         <v>44</v>
@@ -5559,8 +5583,8 @@
       <c r="D101">
         <v>7.63003</v>
       </c>
-      <c r="F101">
-        <v>1</v>
+      <c r="F101" t="s">
+        <v>452</v>
       </c>
       <c r="H101">
         <v>51</v>
@@ -5615,8 +5639,8 @@
       <c r="D102">
         <v>7.187</v>
       </c>
-      <c r="F102">
-        <v>6</v>
+      <c r="F102" t="s">
+        <v>453</v>
       </c>
       <c r="H102">
         <v>24.2</v>
@@ -5674,8 +5698,8 @@
       <c r="E103">
         <v>8</v>
       </c>
-      <c r="F103">
-        <v>5</v>
+      <c r="F103" t="s">
+        <v>459</v>
       </c>
       <c r="H103">
         <v>15.2</v>
@@ -5724,8 +5748,8 @@
       <c r="D104">
         <v>6.985010000000001</v>
       </c>
-      <c r="F104">
-        <v>8</v>
+      <c r="F104" t="s">
+        <v>455</v>
       </c>
       <c r="H104">
         <v>36</v>
@@ -5780,8 +5804,8 @@
       <c r="E105">
         <v>8.4</v>
       </c>
-      <c r="F105">
-        <v>6</v>
+      <c r="F105" t="s">
+        <v>453</v>
       </c>
       <c r="H105">
         <v>14.7</v>
@@ -5836,8 +5860,8 @@
       <c r="D106">
         <v>9.42666</v>
       </c>
-      <c r="F106">
-        <v>1</v>
+      <c r="F106" t="s">
+        <v>452</v>
       </c>
       <c r="H106">
         <v>17.2</v>
@@ -5892,8 +5916,8 @@
       <c r="E107">
         <v>7</v>
       </c>
-      <c r="F107">
-        <v>6</v>
+      <c r="F107" t="s">
+        <v>453</v>
       </c>
       <c r="H107">
         <v>25</v>
@@ -5948,8 +5972,8 @@
       <c r="D108">
         <v>8.959</v>
       </c>
-      <c r="F108">
-        <v>8</v>
+      <c r="F108" t="s">
+        <v>455</v>
       </c>
       <c r="H108">
         <v>13.5</v>
@@ -6001,8 +6025,8 @@
       <c r="D109">
         <v>6.900930000000002</v>
       </c>
-      <c r="F109">
-        <v>5</v>
+      <c r="F109" t="s">
+        <v>459</v>
       </c>
       <c r="H109">
         <v>29.5</v>
@@ -6057,8 +6081,8 @@
       <c r="D110">
         <v>6.900930000000002</v>
       </c>
-      <c r="F110">
-        <v>5</v>
+      <c r="F110" t="s">
+        <v>459</v>
       </c>
       <c r="H110">
         <v>23.1</v>
@@ -6113,8 +6137,8 @@
       <c r="D111">
         <v>7.235580000000001</v>
       </c>
-      <c r="F111">
-        <v>3</v>
+      <c r="F111" t="s">
+        <v>454</v>
       </c>
       <c r="H111">
         <v>17.4</v>
@@ -6172,8 +6196,8 @@
       <c r="E112">
         <v>47</v>
       </c>
-      <c r="F112">
-        <v>1</v>
+      <c r="F112" t="s">
+        <v>452</v>
       </c>
       <c r="H112">
         <v>24.9</v>
@@ -6225,8 +6249,8 @@
       <c r="D113">
         <v>8.991515</v>
       </c>
-      <c r="F113">
-        <v>8</v>
+      <c r="F113" t="s">
+        <v>455</v>
       </c>
       <c r="H113">
         <v>9.6</v>
@@ -6281,8 +6305,8 @@
       <c r="D114">
         <v>8.958349999999999</v>
       </c>
-      <c r="F114">
-        <v>8</v>
+      <c r="F114" t="s">
+        <v>455</v>
       </c>
       <c r="H114">
         <v>8.4</v>
@@ -6337,8 +6361,8 @@
       <c r="D115">
         <v>11.46095773</v>
       </c>
-      <c r="F115">
-        <v>8</v>
+      <c r="F115" t="s">
+        <v>455</v>
       </c>
       <c r="H115">
         <v>21.6</v>
@@ -6360,8 +6384,8 @@
       <c r="D116">
         <v>12.16622997</v>
       </c>
-      <c r="F116">
-        <v>8</v>
+      <c r="F116" t="s">
+        <v>455</v>
       </c>
       <c r="H116">
         <v>38.8</v>
@@ -6383,8 +6407,8 @@
       <c r="D117">
         <v>16.229269</v>
       </c>
-      <c r="F117">
-        <v>5</v>
+      <c r="F117" t="s">
+        <v>459</v>
       </c>
       <c r="H117">
         <v>30.9</v>
@@ -6442,8 +6466,8 @@
       <c r="D118">
         <v>16.229269</v>
       </c>
-      <c r="F118">
-        <v>5</v>
+      <c r="F118" t="s">
+        <v>459</v>
       </c>
       <c r="H118">
         <v>31.5</v>
@@ -6498,8 +6522,8 @@
       <c r="D119">
         <v>16.229269</v>
       </c>
-      <c r="F119">
-        <v>5</v>
+      <c r="F119" t="s">
+        <v>459</v>
       </c>
       <c r="H119">
         <v>24.8</v>
@@ -6551,8 +6575,8 @@
       <c r="D120">
         <v>16.229269</v>
       </c>
-      <c r="F120">
-        <v>5</v>
+      <c r="F120" t="s">
+        <v>459</v>
       </c>
       <c r="H120">
         <v>29</v>
@@ -6604,8 +6628,8 @@
       <c r="D121">
         <v>16.229269</v>
       </c>
-      <c r="F121">
-        <v>5</v>
+      <c r="F121" t="s">
+        <v>459</v>
       </c>
       <c r="H121">
         <v>34.8</v>
@@ -6657,8 +6681,8 @@
       <c r="D122">
         <v>16.229269</v>
       </c>
-      <c r="F122">
-        <v>5</v>
+      <c r="F122" t="s">
+        <v>459</v>
       </c>
       <c r="H122">
         <v>34.6</v>
@@ -6710,8 +6734,8 @@
       <c r="D123">
         <v>16.229269</v>
       </c>
-      <c r="F123">
-        <v>5</v>
+      <c r="F123" t="s">
+        <v>459</v>
       </c>
       <c r="H123">
         <v>33.8</v>
@@ -6760,8 +6784,8 @@
       <c r="D124">
         <v>16.229269</v>
       </c>
-      <c r="F124">
-        <v>5</v>
+      <c r="F124" t="s">
+        <v>459</v>
       </c>
       <c r="H124">
         <v>32.1</v>
@@ -6813,8 +6837,8 @@
       <c r="D125">
         <v>16.323575</v>
       </c>
-      <c r="F125">
-        <v>5</v>
+      <c r="F125" t="s">
+        <v>459</v>
       </c>
       <c r="H125">
         <v>37.3</v>
@@ -6866,8 +6890,8 @@
       <c r="D126">
         <v>16.2128</v>
       </c>
-      <c r="F126">
-        <v>5</v>
+      <c r="F126" t="s">
+        <v>459</v>
       </c>
       <c r="H126">
         <v>22.1</v>
@@ -6919,8 +6943,8 @@
       <c r="D127">
         <v>16.1647</v>
       </c>
-      <c r="F127">
-        <v>5</v>
+      <c r="F127" t="s">
+        <v>459</v>
       </c>
       <c r="H127">
         <v>16.3</v>
@@ -6975,8 +6999,8 @@
       <c r="D128">
         <v>11.6831</v>
       </c>
-      <c r="F128">
-        <v>6</v>
+      <c r="F128" t="s">
+        <v>453</v>
       </c>
       <c r="H128">
         <v>18.1</v>
@@ -7016,8 +7040,8 @@
       <c r="D129">
         <v>11.6831</v>
       </c>
-      <c r="F129">
-        <v>6</v>
+      <c r="F129" t="s">
+        <v>453</v>
       </c>
       <c r="H129">
         <v>20.2</v>
@@ -7057,8 +7081,8 @@
       <c r="D130">
         <v>11.6831</v>
       </c>
-      <c r="F130">
-        <v>6</v>
+      <c r="F130" t="s">
+        <v>453</v>
       </c>
       <c r="H130">
         <v>21.5</v>
@@ -7098,8 +7122,8 @@
       <c r="D131">
         <v>11.6831</v>
       </c>
-      <c r="F131">
-        <v>6</v>
+      <c r="F131" t="s">
+        <v>453</v>
       </c>
       <c r="H131">
         <v>22.1</v>
@@ -7139,8 +7163,8 @@
       <c r="D132">
         <v>13.1365</v>
       </c>
-      <c r="F132">
-        <v>9</v>
+      <c r="F132" t="s">
+        <v>456</v>
       </c>
       <c r="H132">
         <v>36.3</v>
@@ -7183,8 +7207,8 @@
       <c r="D133">
         <v>13.1365</v>
       </c>
-      <c r="F133">
-        <v>9</v>
+      <c r="F133" t="s">
+        <v>456</v>
       </c>
       <c r="H133">
         <v>42.4</v>
@@ -7227,8 +7251,8 @@
       <c r="D134">
         <v>13.1365</v>
       </c>
-      <c r="F134">
-        <v>9</v>
+      <c r="F134" t="s">
+        <v>456</v>
       </c>
       <c r="H134">
         <v>38.1</v>
@@ -7271,8 +7295,8 @@
       <c r="D135">
         <v>13.1365</v>
       </c>
-      <c r="F135">
-        <v>9</v>
+      <c r="F135" t="s">
+        <v>456</v>
       </c>
       <c r="H135">
         <v>36.8</v>
@@ -7315,8 +7339,8 @@
       <c r="D136">
         <v>13.1365</v>
       </c>
-      <c r="F136">
-        <v>9</v>
+      <c r="F136" t="s">
+        <v>456</v>
       </c>
       <c r="H136">
         <v>38.1</v>
@@ -7359,8 +7383,8 @@
       <c r="D137">
         <v>13.1365</v>
       </c>
-      <c r="F137">
-        <v>9</v>
+      <c r="F137" t="s">
+        <v>456</v>
       </c>
       <c r="H137">
         <v>37</v>
@@ -7403,8 +7427,8 @@
       <c r="D138">
         <v>13.1365</v>
       </c>
-      <c r="F138">
-        <v>9</v>
+      <c r="F138" t="s">
+        <v>456</v>
       </c>
       <c r="H138">
         <v>23</v>
@@ -7447,8 +7471,8 @@
       <c r="D139">
         <v>13.1365</v>
       </c>
-      <c r="F139">
-        <v>9</v>
+      <c r="F139" t="s">
+        <v>456</v>
       </c>
       <c r="H139">
         <v>16.1</v>
@@ -7491,8 +7515,8 @@
       <c r="D140">
         <v>13.1365</v>
       </c>
-      <c r="F140">
-        <v>9</v>
+      <c r="F140" t="s">
+        <v>456</v>
       </c>
       <c r="H140">
         <v>45</v>
@@ -7547,8 +7571,8 @@
       <c r="D141">
         <v>13.1365</v>
       </c>
-      <c r="F141">
-        <v>9</v>
+      <c r="F141" t="s">
+        <v>456</v>
       </c>
       <c r="H141">
         <v>44</v>
@@ -7606,8 +7630,8 @@
       <c r="D142">
         <v>13.1365</v>
       </c>
-      <c r="F142">
-        <v>9</v>
+      <c r="F142" t="s">
+        <v>456</v>
       </c>
       <c r="H142">
         <v>47</v>
@@ -7665,8 +7689,8 @@
       <c r="D143">
         <v>15.3653</v>
       </c>
-      <c r="F143">
-        <v>5</v>
+      <c r="F143" t="s">
+        <v>459</v>
       </c>
       <c r="H143">
         <v>27.2</v>
@@ -7718,8 +7742,8 @@
       <c r="D144">
         <v>15.3653</v>
       </c>
-      <c r="F144">
-        <v>5</v>
+      <c r="F144" t="s">
+        <v>459</v>
       </c>
       <c r="H144">
         <v>24.1</v>
@@ -7771,8 +7795,8 @@
       <c r="D145">
         <v>13.826</v>
       </c>
-      <c r="F145">
-        <v>6</v>
+      <c r="F145" t="s">
+        <v>453</v>
       </c>
       <c r="H145">
         <v>31</v>
@@ -7818,8 +7842,8 @@
       <c r="D146">
         <v>13.826</v>
       </c>
-      <c r="F146">
-        <v>6</v>
+      <c r="F146" t="s">
+        <v>453</v>
       </c>
       <c r="H146">
         <v>28</v>
@@ -7841,8 +7865,8 @@
       <c r="D147">
         <v>13.826</v>
       </c>
-      <c r="F147">
-        <v>6</v>
+      <c r="F147" t="s">
+        <v>453</v>
       </c>
       <c r="H147">
         <v>28.5</v>
@@ -7894,8 +7918,8 @@
       <c r="D148">
         <v>13.826</v>
       </c>
-      <c r="F148">
-        <v>6</v>
+      <c r="F148" t="s">
+        <v>453</v>
       </c>
       <c r="H148">
         <v>28.5</v>
@@ -7917,8 +7941,8 @@
       <c r="D149">
         <v>13.826</v>
       </c>
-      <c r="F149">
-        <v>6</v>
+      <c r="F149" t="s">
+        <v>453</v>
       </c>
       <c r="H149">
         <v>25</v>
@@ -7970,8 +7994,8 @@
       <c r="D150">
         <v>13.826</v>
       </c>
-      <c r="F150">
-        <v>6</v>
+      <c r="F150" t="s">
+        <v>453</v>
       </c>
       <c r="H150">
         <v>25</v>
@@ -8023,8 +8047,8 @@
       <c r="D151">
         <v>13.826</v>
       </c>
-      <c r="F151">
-        <v>6</v>
+      <c r="F151" t="s">
+        <v>453</v>
       </c>
       <c r="H151">
         <v>25.65</v>
@@ -8076,8 +8100,8 @@
       <c r="D152">
         <v>13.826</v>
       </c>
-      <c r="F152">
-        <v>6</v>
+      <c r="F152" t="s">
+        <v>453</v>
       </c>
       <c r="H152">
         <v>25.5</v>
@@ -8126,8 +8150,8 @@
       <c r="D153">
         <v>10.5178</v>
       </c>
-      <c r="F153">
-        <v>6</v>
+      <c r="F153" t="s">
+        <v>453</v>
       </c>
       <c r="H153">
         <v>17.6</v>
@@ -8167,8 +8191,8 @@
       <c r="D154">
         <v>16.4728</v>
       </c>
-      <c r="F154">
-        <v>5</v>
+      <c r="F154" t="s">
+        <v>459</v>
       </c>
       <c r="H154">
         <v>24.3</v>
@@ -8220,8 +8244,8 @@
       <c r="D155">
         <v>16.6078</v>
       </c>
-      <c r="F155">
-        <v>5</v>
+      <c r="F155" t="s">
+        <v>459</v>
       </c>
       <c r="H155">
         <v>22.8</v>
@@ -8267,8 +8291,8 @@
       <c r="D156">
         <v>14.3315</v>
       </c>
-      <c r="F156">
-        <v>5</v>
+      <c r="F156" t="s">
+        <v>459</v>
       </c>
       <c r="H156">
         <v>8</v>
@@ -8290,8 +8314,8 @@
       <c r="D157">
         <v>14.256649</v>
       </c>
-      <c r="F157">
-        <v>5</v>
+      <c r="F157" t="s">
+        <v>459</v>
       </c>
       <c r="H157">
         <v>11.5</v>
@@ -8349,8 +8373,8 @@
       <c r="E158">
         <v>6</v>
       </c>
-      <c r="F158">
-        <v>5</v>
+      <c r="F158" t="s">
+        <v>459</v>
       </c>
       <c r="H158">
         <v>25.6</v>
@@ -8405,8 +8429,8 @@
       <c r="D159">
         <v>13.1518</v>
       </c>
-      <c r="F159">
-        <v>6</v>
+      <c r="F159" t="s">
+        <v>453</v>
       </c>
       <c r="H159">
         <v>11.5</v>
@@ -8449,8 +8473,8 @@
       <c r="D160">
         <v>13.4225</v>
       </c>
-      <c r="F160">
-        <v>5</v>
+      <c r="F160" t="s">
+        <v>459</v>
       </c>
       <c r="H160">
         <v>12.25</v>
@@ -8502,8 +8526,8 @@
       <c r="D161">
         <v>13.4225</v>
       </c>
-      <c r="F161">
-        <v>5</v>
+      <c r="F161" t="s">
+        <v>459</v>
       </c>
       <c r="H161">
         <v>11.3</v>
@@ -8555,8 +8579,8 @@
       <c r="D162">
         <v>11.1851</v>
       </c>
-      <c r="F162">
-        <v>6</v>
+      <c r="F162" t="s">
+        <v>453</v>
       </c>
       <c r="H162">
         <v>11.3</v>
@@ -8602,8 +8626,8 @@
       <c r="D163">
         <v>9.6715</v>
       </c>
-      <c r="F163">
-        <v>6</v>
+      <c r="F163" t="s">
+        <v>453</v>
       </c>
       <c r="H163">
         <v>15.6</v>
@@ -8643,8 +8667,8 @@
       <c r="D164">
         <v>10.242</v>
       </c>
-      <c r="F164">
-        <v>6</v>
+      <c r="F164" t="s">
+        <v>453</v>
       </c>
       <c r="H164">
         <v>8.800000000000001</v>
@@ -8681,8 +8705,8 @@
       <c r="D165">
         <v>9.7997</v>
       </c>
-      <c r="F165">
-        <v>8</v>
+      <c r="F165" t="s">
+        <v>455</v>
       </c>
       <c r="H165">
         <v>14.2</v>
@@ -8725,8 +8749,8 @@
       <c r="D166">
         <v>9.913399999999999</v>
       </c>
-      <c r="F166">
-        <v>5</v>
+      <c r="F166" t="s">
+        <v>459</v>
       </c>
       <c r="H166">
         <v>4.1</v>
@@ -8763,8 +8787,8 @@
       <c r="D167">
         <v>14.1295</v>
       </c>
-      <c r="F167">
-        <v>6</v>
+      <c r="F167" t="s">
+        <v>453</v>
       </c>
       <c r="H167">
         <v>7</v>
@@ -8813,8 +8837,8 @@
       <c r="D168">
         <v>14.5693</v>
       </c>
-      <c r="F168">
-        <v>8</v>
+      <c r="F168" t="s">
+        <v>455</v>
       </c>
       <c r="H168">
         <v>15.7</v>
@@ -8872,8 +8896,8 @@
       <c r="D169">
         <v>14.5693</v>
       </c>
-      <c r="F169">
-        <v>8</v>
+      <c r="F169" t="s">
+        <v>455</v>
       </c>
       <c r="H169">
         <v>14.7</v>
@@ -8928,8 +8952,8 @@
       <c r="D170">
         <v>14.8025</v>
       </c>
-      <c r="F170">
-        <v>8</v>
+      <c r="F170" t="s">
+        <v>455</v>
       </c>
       <c r="H170">
         <v>7.7</v>
@@ -8969,8 +8993,8 @@
       <c r="D171">
         <v>14.8025</v>
       </c>
-      <c r="F171">
-        <v>8</v>
+      <c r="F171" t="s">
+        <v>455</v>
       </c>
       <c r="H171">
         <v>9.9</v>
@@ -9019,8 +9043,8 @@
       <c r="D172">
         <v>10.9657</v>
       </c>
-      <c r="F172">
-        <v>8</v>
+      <c r="F172" t="s">
+        <v>455</v>
       </c>
       <c r="H172">
         <v>11.4</v>
@@ -9063,8 +9087,8 @@
       <c r="D173">
         <v>10.9657</v>
       </c>
-      <c r="F173">
-        <v>8</v>
+      <c r="F173" t="s">
+        <v>455</v>
       </c>
       <c r="H173">
         <v>7.4</v>
@@ -9104,8 +9128,8 @@
       <c r="D174">
         <v>14.5928</v>
       </c>
-      <c r="F174">
-        <v>8</v>
+      <c r="F174" t="s">
+        <v>455</v>
       </c>
       <c r="H174">
         <v>7.4</v>
@@ -9139,8 +9163,8 @@
       <c r="D175">
         <v>12.7669</v>
       </c>
-      <c r="F175">
-        <v>8</v>
+      <c r="F175" t="s">
+        <v>455</v>
       </c>
       <c r="H175">
         <v>12.3</v>
@@ -9180,8 +9204,8 @@
       <c r="D176">
         <v>13.1689</v>
       </c>
-      <c r="F176">
-        <v>8</v>
+      <c r="F176" t="s">
+        <v>455</v>
       </c>
       <c r="H176">
         <v>8.9</v>
@@ -9230,8 +9254,8 @@
       <c r="D177">
         <v>13.1689</v>
       </c>
-      <c r="F177">
-        <v>8</v>
+      <c r="F177" t="s">
+        <v>455</v>
       </c>
       <c r="H177">
         <v>5.3</v>
@@ -9280,8 +9304,8 @@
       <c r="D178">
         <v>13.5148</v>
       </c>
-      <c r="F178">
-        <v>8</v>
+      <c r="F178" t="s">
+        <v>455</v>
       </c>
       <c r="H178">
         <v>11.6</v>
@@ -9330,8 +9354,8 @@
       <c r="D179">
         <v>13.5028</v>
       </c>
-      <c r="F179">
-        <v>8</v>
+      <c r="F179" t="s">
+        <v>455</v>
       </c>
       <c r="H179">
         <v>11</v>
@@ -9371,8 +9395,8 @@
       <c r="D180">
         <v>10.6436</v>
       </c>
-      <c r="F180">
-        <v>8</v>
+      <c r="F180" t="s">
+        <v>455</v>
       </c>
       <c r="H180">
         <v>6.6</v>
@@ -9427,8 +9451,8 @@
       <c r="D181">
         <v>10.6626</v>
       </c>
-      <c r="F181">
-        <v>8</v>
+      <c r="F181" t="s">
+        <v>455</v>
       </c>
       <c r="H181">
         <v>9.6</v>
@@ -9480,8 +9504,8 @@
       <c r="D182">
         <v>9.979100000000001</v>
       </c>
-      <c r="F182">
-        <v>6</v>
+      <c r="F182" t="s">
+        <v>453</v>
       </c>
       <c r="H182">
         <v>11.9</v>
@@ -9521,8 +9545,8 @@
       <c r="D183">
         <v>9.9017</v>
       </c>
-      <c r="F183">
-        <v>6</v>
+      <c r="F183" t="s">
+        <v>453</v>
       </c>
       <c r="H183">
         <v>12.3</v>
@@ -9559,8 +9583,8 @@
       <c r="D184">
         <v>13.0571</v>
       </c>
-      <c r="F184">
-        <v>8</v>
+      <c r="F184" t="s">
+        <v>455</v>
       </c>
       <c r="H184">
         <v>10.9</v>
@@ -9597,8 +9621,8 @@
       <c r="D185">
         <v>15.32</v>
       </c>
-      <c r="F185">
-        <v>8</v>
+      <c r="F185" t="s">
+        <v>455</v>
       </c>
       <c r="H185">
         <v>10.8</v>
@@ -9656,8 +9680,8 @@
       <c r="E186">
         <v>8</v>
       </c>
-      <c r="F186">
-        <v>6</v>
+      <c r="F186" t="s">
+        <v>453</v>
       </c>
       <c r="H186">
         <v>24.3</v>
@@ -9715,8 +9739,8 @@
       <c r="E187">
         <v>53.1</v>
       </c>
-      <c r="F187">
-        <v>6</v>
+      <c r="F187" t="s">
+        <v>453</v>
       </c>
       <c r="H187">
         <v>22.5</v>
@@ -9768,8 +9792,8 @@
       <c r="E188">
         <v>8</v>
       </c>
-      <c r="F188">
-        <v>6</v>
+      <c r="F188" t="s">
+        <v>453</v>
       </c>
       <c r="H188">
         <v>21.3</v>
@@ -9827,8 +9851,8 @@
       <c r="E189">
         <v>7.75</v>
       </c>
-      <c r="F189">
-        <v>6</v>
+      <c r="F189" t="s">
+        <v>453</v>
       </c>
       <c r="H189">
         <v>24.5</v>
@@ -9886,8 +9910,8 @@
       <c r="E190">
         <v>12</v>
       </c>
-      <c r="F190">
-        <v>6</v>
+      <c r="F190" t="s">
+        <v>453</v>
       </c>
       <c r="H190">
         <v>20.3</v>
@@ -9942,8 +9966,8 @@
       <c r="E191">
         <v>15</v>
       </c>
-      <c r="F191">
-        <v>5</v>
+      <c r="F191" t="s">
+        <v>459</v>
       </c>
       <c r="H191">
         <v>11.8</v>
@@ -9965,8 +9989,8 @@
       <c r="D192">
         <v>14.986191</v>
       </c>
-      <c r="F192">
-        <v>6</v>
+      <c r="F192" t="s">
+        <v>453</v>
       </c>
       <c r="H192">
         <v>17.5</v>
@@ -10021,8 +10045,8 @@
       <c r="D193">
         <v>14.783171</v>
       </c>
-      <c r="F193">
-        <v>5</v>
+      <c r="F193" t="s">
+        <v>459</v>
       </c>
       <c r="H193">
         <v>24</v>
@@ -10077,8 +10101,8 @@
       <c r="D194">
         <v>13.629066</v>
       </c>
-      <c r="F194">
-        <v>6</v>
+      <c r="F194" t="s">
+        <v>453</v>
       </c>
       <c r="H194">
         <v>18.5</v>
@@ -10133,8 +10157,8 @@
       <c r="D195">
         <v>12.117442</v>
       </c>
-      <c r="F195">
-        <v>6</v>
+      <c r="F195" t="s">
+        <v>453</v>
       </c>
       <c r="H195">
         <v>14.5</v>
@@ -10192,8 +10216,8 @@
       <c r="D196">
         <v>13.782635</v>
       </c>
-      <c r="F196">
-        <v>6</v>
+      <c r="F196" t="s">
+        <v>453</v>
       </c>
       <c r="H196">
         <v>22.9</v>
@@ -10245,8 +10269,8 @@
       <c r="D197">
         <v>13.191587</v>
       </c>
-      <c r="F197">
-        <v>8</v>
+      <c r="F197" t="s">
+        <v>455</v>
       </c>
       <c r="H197">
         <v>15.2</v>
@@ -10298,8 +10322,8 @@
       <c r="E198">
         <v>5.2</v>
       </c>
-      <c r="F198">
-        <v>5</v>
+      <c r="F198" t="s">
+        <v>459</v>
       </c>
       <c r="H198">
         <v>14</v>
@@ -10363,8 +10387,8 @@
       <c r="E199">
         <v>6</v>
       </c>
-      <c r="F199">
-        <v>5</v>
+      <c r="F199" t="s">
+        <v>459</v>
       </c>
       <c r="H199">
         <v>19.6</v>
@@ -10416,8 +10440,8 @@
       <c r="E200">
         <v>22.5</v>
       </c>
-      <c r="F200">
-        <v>5</v>
+      <c r="F200" t="s">
+        <v>459</v>
       </c>
       <c r="H200">
         <v>14.2</v>
@@ -10478,8 +10502,8 @@
       <c r="E201">
         <v>85</v>
       </c>
-      <c r="F201">
-        <v>5</v>
+      <c r="F201" t="s">
+        <v>459</v>
       </c>
       <c r="H201">
         <v>13.9</v>
@@ -10534,8 +10558,8 @@
       <c r="E202">
         <v>86.42</v>
       </c>
-      <c r="F202">
-        <v>8</v>
+      <c r="F202" t="s">
+        <v>455</v>
       </c>
       <c r="H202">
         <v>12.95</v>
@@ -10593,8 +10617,8 @@
       <c r="E203">
         <v>100</v>
       </c>
-      <c r="F203">
-        <v>8</v>
+      <c r="F203" t="s">
+        <v>455</v>
       </c>
       <c r="H203">
         <v>12.6</v>
@@ -10655,8 +10679,8 @@
       <c r="E204">
         <v>30</v>
       </c>
-      <c r="F204">
-        <v>8</v>
+      <c r="F204" t="s">
+        <v>455</v>
       </c>
       <c r="H204">
         <v>13</v>
@@ -10717,8 +10741,8 @@
       <c r="D205">
         <v>14.802535</v>
       </c>
-      <c r="F205">
-        <v>8</v>
+      <c r="F205" t="s">
+        <v>455</v>
       </c>
       <c r="H205">
         <v>9.85</v>
@@ -10773,8 +10797,8 @@
       <c r="D206">
         <v>14.814508</v>
       </c>
-      <c r="F206">
-        <v>8</v>
+      <c r="F206" t="s">
+        <v>455</v>
       </c>
       <c r="H206">
         <v>10.3</v>
@@ -10829,8 +10853,8 @@
       <c r="D207">
         <v>14.777709</v>
       </c>
-      <c r="F207">
-        <v>8</v>
+      <c r="F207" t="s">
+        <v>455</v>
       </c>
       <c r="H207">
         <v>9.800000000000001</v>
@@ -10879,8 +10903,8 @@
       <c r="D208">
         <v>14.783736</v>
       </c>
-      <c r="F208">
-        <v>8</v>
+      <c r="F208" t="s">
+        <v>455</v>
       </c>
       <c r="H208">
         <v>9.9</v>
@@ -10932,8 +10956,8 @@
       <c r="D209">
         <v>14.760945</v>
       </c>
-      <c r="F209">
-        <v>8</v>
+      <c r="F209" t="s">
+        <v>455</v>
       </c>
       <c r="H209">
         <v>10.8</v>
@@ -10988,8 +11012,8 @@
       <c r="D210">
         <v>14.59296</v>
       </c>
-      <c r="F210">
-        <v>9</v>
+      <c r="F210" t="s">
+        <v>456</v>
       </c>
       <c r="H210">
         <v>10.1</v>
@@ -11044,8 +11068,8 @@
       <c r="D211">
         <v>14.59296</v>
       </c>
-      <c r="F211">
-        <v>9</v>
+      <c r="F211" t="s">
+        <v>456</v>
       </c>
       <c r="H211">
         <v>9.699999999999999</v>
@@ -11100,8 +11124,8 @@
       <c r="D212">
         <v>14.516993</v>
       </c>
-      <c r="F212">
-        <v>8</v>
+      <c r="F212" t="s">
+        <v>455</v>
       </c>
       <c r="H212">
         <v>7.5</v>
@@ -11153,8 +11177,8 @@
       <c r="D213">
         <v>14.5481</v>
       </c>
-      <c r="F213">
-        <v>6</v>
+      <c r="F213" t="s">
+        <v>453</v>
       </c>
       <c r="H213">
         <v>8.199999999999999</v>
@@ -11206,8 +11230,8 @@
       <c r="D214">
         <v>14.5481</v>
       </c>
-      <c r="F214">
-        <v>6</v>
+      <c r="F214" t="s">
+        <v>453</v>
       </c>
       <c r="H214">
         <v>8.6</v>
@@ -11259,8 +11283,8 @@
       <c r="D215">
         <v>14.536693</v>
       </c>
-      <c r="F215">
-        <v>6</v>
+      <c r="F215" t="s">
+        <v>453</v>
       </c>
       <c r="H215">
         <v>7.5</v>
@@ -11315,8 +11339,8 @@
       <c r="D216">
         <v>14.536693</v>
       </c>
-      <c r="F216">
-        <v>6</v>
+      <c r="F216" t="s">
+        <v>453</v>
       </c>
       <c r="H216">
         <v>7.3</v>
@@ -11374,8 +11398,8 @@
       <c r="D217">
         <v>14.557603</v>
       </c>
-      <c r="F217">
-        <v>6</v>
+      <c r="F217" t="s">
+        <v>453</v>
       </c>
       <c r="H217">
         <v>8.5</v>
@@ -11424,8 +11448,8 @@
       <c r="D218">
         <v>13.060723</v>
       </c>
-      <c r="F218">
-        <v>8</v>
+      <c r="F218" t="s">
+        <v>455</v>
       </c>
       <c r="H218">
         <v>10.2</v>
@@ -11474,8 +11498,8 @@
       <c r="D219">
         <v>13.194507</v>
       </c>
-      <c r="F219">
-        <v>6</v>
+      <c r="F219" t="s">
+        <v>453</v>
       </c>
       <c r="H219">
         <v>11.3</v>
@@ -11533,8 +11557,8 @@
       <c r="D220">
         <v>13.053921</v>
       </c>
-      <c r="F220">
-        <v>8</v>
+      <c r="F220" t="s">
+        <v>455</v>
       </c>
       <c r="H220">
         <v>9.300000000000001</v>
@@ -11592,8 +11616,8 @@
       <c r="D221">
         <v>13.035942</v>
       </c>
-      <c r="F221">
-        <v>6</v>
+      <c r="F221" t="s">
+        <v>453</v>
       </c>
       <c r="H221">
         <v>10.7</v>
@@ -11651,8 +11675,8 @@
       <c r="D222">
         <v>12.768106</v>
       </c>
-      <c r="F222">
-        <v>8</v>
+      <c r="F222" t="s">
+        <v>455</v>
       </c>
       <c r="H222">
         <v>12.5</v>
@@ -11710,8 +11734,8 @@
       <c r="D223">
         <v>12.766167</v>
       </c>
-      <c r="F223">
-        <v>8</v>
+      <c r="F223" t="s">
+        <v>455</v>
       </c>
       <c r="H223">
         <v>13.1</v>
@@ -11769,8 +11793,8 @@
       <c r="D224">
         <v>13.50178</v>
       </c>
-      <c r="F224">
-        <v>8</v>
+      <c r="F224" t="s">
+        <v>455</v>
       </c>
       <c r="H224">
         <v>16</v>
@@ -11822,8 +11846,8 @@
       <c r="D225">
         <v>13.495442</v>
       </c>
-      <c r="F225">
-        <v>8</v>
+      <c r="F225" t="s">
+        <v>455</v>
       </c>
       <c r="H225">
         <v>10.8</v>
@@ -11881,8 +11905,8 @@
       <c r="E226">
         <v>94</v>
       </c>
-      <c r="F226">
-        <v>6</v>
+      <c r="F226" t="s">
+        <v>453</v>
       </c>
       <c r="H226">
         <v>36.5</v>
@@ -11937,8 +11961,8 @@
       <c r="E227">
         <v>5</v>
       </c>
-      <c r="F227">
-        <v>6</v>
+      <c r="F227" t="s">
+        <v>453</v>
       </c>
       <c r="H227">
         <v>11.4</v>
@@ -12002,8 +12026,8 @@
       <c r="E228">
         <v>5</v>
       </c>
-      <c r="F228">
-        <v>6</v>
+      <c r="F228" t="s">
+        <v>453</v>
       </c>
       <c r="H228">
         <v>10.3</v>
@@ -12067,8 +12091,8 @@
       <c r="E229">
         <v>5</v>
       </c>
-      <c r="F229">
-        <v>6</v>
+      <c r="F229" t="s">
+        <v>453</v>
       </c>
       <c r="H229">
         <v>10.6</v>
@@ -12132,8 +12156,8 @@
       <c r="E230">
         <v>92</v>
       </c>
-      <c r="F230">
-        <v>8</v>
+      <c r="F230" t="s">
+        <v>455</v>
       </c>
       <c r="H230">
         <v>13.6</v>
@@ -12191,8 +12215,8 @@
       <c r="D231">
         <v>13.690503</v>
       </c>
-      <c r="F231">
-        <v>8</v>
+      <c r="F231" t="s">
+        <v>455</v>
       </c>
       <c r="H231">
         <v>9.800000000000001</v>
@@ -12241,8 +12265,8 @@
       <c r="D232">
         <v>12.507543</v>
       </c>
-      <c r="F232">
-        <v>8</v>
+      <c r="F232" t="s">
+        <v>455</v>
       </c>
       <c r="H232">
         <v>15</v>
@@ -12297,8 +12321,8 @@
       <c r="D233">
         <v>15.194748</v>
       </c>
-      <c r="F233">
-        <v>8</v>
+      <c r="F233" t="s">
+        <v>455</v>
       </c>
       <c r="H233">
         <v>13</v>
@@ -12350,8 +12374,8 @@
       <c r="E234">
         <v>9</v>
       </c>
-      <c r="F234">
-        <v>8</v>
+      <c r="F234" t="s">
+        <v>455</v>
       </c>
       <c r="H234">
         <v>10</v>
@@ -12412,8 +12436,8 @@
       <c r="E235">
         <v>7.2</v>
       </c>
-      <c r="F235">
-        <v>8</v>
+      <c r="F235" t="s">
+        <v>455</v>
       </c>
       <c r="H235">
         <v>13.5</v>
@@ -12468,8 +12492,8 @@
       <c r="D236">
         <v>15.312227</v>
       </c>
-      <c r="F236">
-        <v>8</v>
+      <c r="F236" t="s">
+        <v>455</v>
       </c>
       <c r="H236">
         <v>10</v>
@@ -12524,8 +12548,8 @@
       <c r="D237">
         <v>14.81086</v>
       </c>
-      <c r="F237">
-        <v>8</v>
+      <c r="F237" t="s">
+        <v>455</v>
       </c>
       <c r="H237">
         <v>10</v>
@@ -12583,8 +12607,8 @@
       <c r="D238">
         <v>14.163093</v>
       </c>
-      <c r="F238">
-        <v>8</v>
+      <c r="F238" t="s">
+        <v>455</v>
       </c>
       <c r="H238">
         <v>8</v>
@@ -12639,8 +12663,8 @@
       <c r="D239">
         <v>14.151461</v>
       </c>
-      <c r="F239">
-        <v>5</v>
+      <c r="F239" t="s">
+        <v>459</v>
       </c>
       <c r="H239">
         <v>6.9</v>
@@ -12695,8 +12719,8 @@
       <c r="D240">
         <v>14.151461</v>
       </c>
-      <c r="F240">
-        <v>5</v>
+      <c r="F240" t="s">
+        <v>459</v>
       </c>
       <c r="H240">
         <v>9.5</v>
@@ -12751,8 +12775,8 @@
       <c r="D241">
         <v>14.151461</v>
       </c>
-      <c r="F241">
-        <v>5</v>
+      <c r="F241" t="s">
+        <v>459</v>
       </c>
       <c r="H241">
         <v>9.800000000000001</v>
@@ -12810,8 +12834,8 @@
       <c r="D242">
         <v>14.151461</v>
       </c>
-      <c r="F242">
-        <v>5</v>
+      <c r="F242" t="s">
+        <v>459</v>
       </c>
       <c r="H242">
         <v>8.699999999999999</v>
@@ -12866,8 +12890,8 @@
       <c r="D243">
         <v>14.151461</v>
       </c>
-      <c r="F243">
-        <v>5</v>
+      <c r="F243" t="s">
+        <v>459</v>
       </c>
       <c r="H243">
         <v>8.699999999999999</v>
@@ -12922,8 +12946,8 @@
       <c r="D244">
         <v>14.151461</v>
       </c>
-      <c r="F244">
-        <v>5</v>
+      <c r="F244" t="s">
+        <v>459</v>
       </c>
       <c r="H244">
         <v>8.6</v>
@@ -12978,8 +13002,8 @@
       <c r="D245">
         <v>11.863071</v>
       </c>
-      <c r="F245">
-        <v>6</v>
+      <c r="F245" t="s">
+        <v>453</v>
       </c>
       <c r="H245">
         <v>9.800000000000001</v>
@@ -13040,8 +13064,8 @@
       <c r="D246">
         <v>6.217712402</v>
       </c>
-      <c r="F246">
-        <v>6</v>
+      <c r="F246" t="s">
+        <v>453</v>
       </c>
       <c r="H246">
         <v>30</v>
@@ -13063,8 +13087,8 @@
       <c r="D247">
         <v>6.550720215</v>
       </c>
-      <c r="F247">
-        <v>6</v>
+      <c r="F247" t="s">
+        <v>453</v>
       </c>
       <c r="H247">
         <v>34.25</v>
@@ -13086,8 +13110,8 @@
       <c r="D248">
         <v>6.463928223</v>
       </c>
-      <c r="F248">
-        <v>3</v>
+      <c r="F248" t="s">
+        <v>454</v>
       </c>
       <c r="H248">
         <v>30</v>
@@ -13109,8 +13133,8 @@
       <c r="D249">
         <v>6.550476074</v>
       </c>
-      <c r="F249">
-        <v>3</v>
+      <c r="F249" t="s">
+        <v>454</v>
       </c>
       <c r="H249">
         <v>37.5</v>
@@ -13132,8 +13156,8 @@
       <c r="D250">
         <v>5.782287598</v>
       </c>
-      <c r="F250">
-        <v>6</v>
+      <c r="F250" t="s">
+        <v>453</v>
       </c>
       <c r="H250">
         <v>58.5</v>
@@ -13155,8 +13179,8 @@
       <c r="D251">
         <v>6.76171875</v>
       </c>
-      <c r="F251">
-        <v>6</v>
+      <c r="F251" t="s">
+        <v>453</v>
       </c>
       <c r="H251">
         <v>32</v>
@@ -13178,8 +13202,8 @@
       <c r="D252">
         <v>5.833496094</v>
       </c>
-      <c r="F252">
-        <v>6</v>
+      <c r="F252" t="s">
+        <v>453</v>
       </c>
       <c r="H252">
         <v>34</v>
@@ -13201,8 +13225,8 @@
       <c r="D253">
         <v>6.067687987999999</v>
       </c>
-      <c r="F253">
-        <v>6</v>
+      <c r="F253" t="s">
+        <v>453</v>
       </c>
       <c r="H253">
         <v>19.5</v>
@@ -13224,8 +13248,8 @@
       <c r="D254">
         <v>7.361083983999999</v>
       </c>
-      <c r="F254">
-        <v>5</v>
+      <c r="F254" t="s">
+        <v>459</v>
       </c>
       <c r="H254">
         <v>30</v>
@@ -13247,8 +13271,8 @@
       <c r="D255">
         <v>5.985107422</v>
       </c>
-      <c r="F255">
-        <v>6</v>
+      <c r="F255" t="s">
+        <v>453</v>
       </c>
       <c r="H255">
         <v>37</v>
@@ -13273,8 +13297,8 @@
       <c r="E256">
         <v>7.45</v>
       </c>
-      <c r="F256">
-        <v>6</v>
+      <c r="F256" t="s">
+        <v>453</v>
       </c>
       <c r="H256">
         <v>39.6</v>
@@ -13329,8 +13353,8 @@
       <c r="D257">
         <v>6.70595</v>
       </c>
-      <c r="F257">
-        <v>6</v>
+      <c r="F257" t="s">
+        <v>453</v>
       </c>
       <c r="H257">
         <v>32.8</v>
@@ -13385,8 +13409,8 @@
       <c r="D258">
         <v>6.70595</v>
       </c>
-      <c r="F258">
-        <v>6</v>
+      <c r="F258" t="s">
+        <v>453</v>
       </c>
       <c r="H258">
         <v>33.6</v>
@@ -13435,8 +13459,8 @@
       <c r="D259">
         <v>6.70611111</v>
       </c>
-      <c r="F259">
-        <v>6</v>
+      <c r="F259" t="s">
+        <v>453</v>
       </c>
       <c r="H259">
         <v>25</v>
@@ -13488,8 +13512,8 @@
       <c r="D260">
         <v>5.44527778</v>
       </c>
-      <c r="F260">
-        <v>5</v>
+      <c r="F260" t="s">
+        <v>459</v>
       </c>
       <c r="H260">
         <v>35.5</v>
@@ -13511,8 +13535,8 @@
       <c r="D261">
         <v>5.44527778</v>
       </c>
-      <c r="F261">
-        <v>5</v>
+      <c r="F261" t="s">
+        <v>459</v>
       </c>
       <c r="H261">
         <v>19</v>
@@ -13534,8 +13558,8 @@
       <c r="D262">
         <v>6.084013</v>
       </c>
-      <c r="F262">
-        <v>8</v>
+      <c r="F262" t="s">
+        <v>455</v>
       </c>
       <c r="H262">
         <v>16.7</v>
@@ -13587,8 +13611,8 @@
       <c r="D263">
         <v>6.54715688</v>
       </c>
-      <c r="F263">
-        <v>3</v>
+      <c r="F263" t="s">
+        <v>454</v>
       </c>
       <c r="H263">
         <v>8</v>
@@ -13640,8 +13664,8 @@
       <c r="D264">
         <v>6.54715688</v>
       </c>
-      <c r="F264">
-        <v>3</v>
+      <c r="F264" t="s">
+        <v>454</v>
       </c>
       <c r="H264">
         <v>13</v>
@@ -13678,8 +13702,8 @@
       <c r="D265">
         <v>7.30982505</v>
       </c>
-      <c r="F265">
-        <v>8</v>
+      <c r="F265" t="s">
+        <v>455</v>
       </c>
       <c r="H265">
         <v>28.95</v>
@@ -13722,8 +13746,8 @@
       <c r="D266">
         <v>7.309825</v>
       </c>
-      <c r="F266">
-        <v>8</v>
+      <c r="F266" t="s">
+        <v>455</v>
       </c>
       <c r="H266">
         <v>22.95</v>
@@ -13766,8 +13790,8 @@
       <c r="D267">
         <v>6.570693449</v>
       </c>
-      <c r="F267">
-        <v>3</v>
+      <c r="F267" t="s">
+        <v>454</v>
       </c>
       <c r="H267">
         <v>35.2</v>
@@ -13792,8 +13816,8 @@
       <c r="E268">
         <v>4.5</v>
       </c>
-      <c r="F268">
-        <v>3</v>
+      <c r="F268" t="s">
+        <v>454</v>
       </c>
       <c r="H268">
         <v>38</v>
@@ -13845,8 +13869,8 @@
       <c r="D269">
         <v>5.988171864</v>
       </c>
-      <c r="F269">
-        <v>6</v>
+      <c r="F269" t="s">
+        <v>453</v>
       </c>
       <c r="H269">
         <v>9.5</v>
@@ -13898,8 +13922,8 @@
       <c r="D270">
         <v>6.878868607</v>
       </c>
-      <c r="F270">
-        <v>6</v>
+      <c r="F270" t="s">
+        <v>453</v>
       </c>
       <c r="H270">
         <v>7.5</v>
@@ -13924,8 +13948,8 @@
       <c r="E271">
         <v>17.1</v>
       </c>
-      <c r="F271">
-        <v>6</v>
+      <c r="F271" t="s">
+        <v>453</v>
       </c>
       <c r="H271">
         <v>10.8</v>
@@ -13956,8 +13980,8 @@
       <c r="E272">
         <v>13.5</v>
       </c>
-      <c r="F272">
-        <v>6</v>
+      <c r="F272" t="s">
+        <v>453</v>
       </c>
       <c r="H272">
         <v>10.2</v>
@@ -14006,8 +14030,8 @@
       <c r="D273">
         <v>6.24789036</v>
       </c>
-      <c r="F273">
-        <v>6</v>
+      <c r="F273" t="s">
+        <v>453</v>
       </c>
       <c r="H273">
         <v>25.2</v>
@@ -14026,8 +14050,8 @@
       <c r="D274">
         <v>6.706080394</v>
       </c>
-      <c r="F274">
-        <v>6</v>
+      <c r="F274" t="s">
+        <v>453</v>
       </c>
       <c r="H274">
         <v>41</v>
@@ -14073,8 +14097,8 @@
       <c r="D275">
         <v>6.359454212</v>
       </c>
-      <c r="F275">
-        <v>6</v>
+      <c r="F275" t="s">
+        <v>453</v>
       </c>
       <c r="H275">
         <v>40</v>
@@ -14120,8 +14144,8 @@
       <c r="E276">
         <v>14</v>
       </c>
-      <c r="F276">
-        <v>6</v>
+      <c r="F276" t="s">
+        <v>453</v>
       </c>
       <c r="H276">
         <v>54</v>
@@ -14146,8 +14170,8 @@
       <c r="E277">
         <v>18.2</v>
       </c>
-      <c r="F277">
-        <v>6</v>
+      <c r="F277" t="s">
+        <v>453</v>
       </c>
       <c r="H277">
         <v>51</v>
@@ -14202,8 +14226,8 @@
       <c r="E278">
         <v>16</v>
       </c>
-      <c r="F278">
-        <v>6</v>
+      <c r="F278" t="s">
+        <v>453</v>
       </c>
       <c r="H278">
         <v>51</v>
@@ -14258,8 +14282,8 @@
       <c r="E279">
         <v>12</v>
       </c>
-      <c r="F279">
-        <v>6</v>
+      <c r="F279" t="s">
+        <v>453</v>
       </c>
       <c r="H279">
         <v>51</v>
@@ -14311,8 +14335,8 @@
       <c r="E280">
         <v>23.95</v>
       </c>
-      <c r="F280">
-        <v>6</v>
+      <c r="F280" t="s">
+        <v>453</v>
       </c>
       <c r="H280">
         <v>49.5</v>
@@ -14367,8 +14391,8 @@
       <c r="E281">
         <v>75</v>
       </c>
-      <c r="F281">
-        <v>5</v>
+      <c r="F281" t="s">
+        <v>459</v>
       </c>
       <c r="H281">
         <v>11.8</v>
@@ -14426,8 +14450,8 @@
       <c r="D282">
         <v>5.44605686</v>
       </c>
-      <c r="F282">
-        <v>6</v>
+      <c r="F282" t="s">
+        <v>453</v>
       </c>
       <c r="H282">
         <v>11.4</v>
@@ -14485,8 +14509,8 @@
       <c r="D283">
         <v>5.455578599999999</v>
       </c>
-      <c r="F283">
-        <v>5</v>
+      <c r="F283" t="s">
+        <v>459</v>
       </c>
       <c r="H283">
         <v>14.6</v>
@@ -14541,8 +14565,8 @@
       <c r="D284">
         <v>5.63828</v>
       </c>
-      <c r="F284">
-        <v>3</v>
+      <c r="F284" t="s">
+        <v>454</v>
       </c>
       <c r="H284">
         <v>58</v>
@@ -14567,8 +14591,8 @@
       <c r="E285">
         <v>7.5</v>
       </c>
-      <c r="F285">
-        <v>6</v>
+      <c r="F285" t="s">
+        <v>453</v>
       </c>
       <c r="H285">
         <v>13</v>
@@ -14590,8 +14614,8 @@
       <c r="D286">
         <v>5.00687996</v>
       </c>
-      <c r="F286">
-        <v>5</v>
+      <c r="F286" t="s">
+        <v>459</v>
       </c>
       <c r="H286">
         <v>25</v>
@@ -14613,8 +14637,8 @@
       <c r="D287">
         <v>6.52881821</v>
       </c>
-      <c r="F287">
-        <v>6</v>
+      <c r="F287" t="s">
+        <v>453</v>
       </c>
       <c r="H287">
         <v>32</v>
@@ -14666,8 +14690,8 @@
       <c r="D288">
         <v>6.52869257</v>
       </c>
-      <c r="F288">
-        <v>6</v>
+      <c r="F288" t="s">
+        <v>453</v>
       </c>
       <c r="H288">
         <v>34</v>
@@ -14719,8 +14743,8 @@
       <c r="D289">
         <v>6.528151253</v>
       </c>
-      <c r="F289">
-        <v>6</v>
+      <c r="F289" t="s">
+        <v>453</v>
       </c>
       <c r="H289">
         <v>33.7</v>
@@ -14745,8 +14769,8 @@
       <c r="E290">
         <v>8</v>
       </c>
-      <c r="F290">
-        <v>3</v>
+      <c r="F290" t="s">
+        <v>454</v>
       </c>
       <c r="H290">
         <v>27</v>
@@ -14801,8 +14825,8 @@
       <c r="D291">
         <v>6.683427</v>
       </c>
-      <c r="F291">
-        <v>6</v>
+      <c r="F291" t="s">
+        <v>453</v>
       </c>
       <c r="H291">
         <v>41.4</v>
@@ -14848,8 +14872,8 @@
       <c r="D292">
         <v>15.2372</v>
       </c>
-      <c r="F292">
-        <v>1</v>
+      <c r="F292" t="s">
+        <v>452</v>
       </c>
       <c r="H292">
         <v>35.3</v>
@@ -14889,8 +14913,8 @@
       <c r="D293">
         <v>15.2283</v>
       </c>
-      <c r="F293">
-        <v>5</v>
+      <c r="F293" t="s">
+        <v>459</v>
       </c>
       <c r="H293">
         <v>35</v>
@@ -14933,8 +14957,8 @@
       <c r="D294">
         <v>14.262091</v>
       </c>
-      <c r="F294">
-        <v>5</v>
+      <c r="F294" t="s">
+        <v>459</v>
       </c>
       <c r="H294">
         <v>19.5</v>
@@ -14974,8 +14998,8 @@
       <c r="D295">
         <v>14.187038</v>
       </c>
-      <c r="F295">
-        <v>7</v>
+      <c r="F295" t="s">
+        <v>454</v>
       </c>
       <c r="H295">
         <v>15.15</v>
@@ -15021,8 +15045,8 @@
       <c r="D296">
         <v>15.0219</v>
       </c>
-      <c r="F296">
-        <v>1</v>
+      <c r="F296" t="s">
+        <v>452</v>
       </c>
       <c r="H296">
         <v>29.5</v>
@@ -15068,8 +15092,8 @@
       <c r="D297">
         <v>14.8715</v>
       </c>
-      <c r="F297">
-        <v>6</v>
+      <c r="F297" t="s">
+        <v>453</v>
       </c>
       <c r="H297">
         <v>15</v>
@@ -15124,8 +15148,8 @@
       <c r="D298">
         <v>14.1891</v>
       </c>
-      <c r="F298">
-        <v>6</v>
+      <c r="F298" t="s">
+        <v>453</v>
       </c>
       <c r="H298">
         <v>13.5</v>
@@ -15177,8 +15201,8 @@
       <c r="D299">
         <v>14.1524</v>
       </c>
-      <c r="F299">
-        <v>1</v>
+      <c r="F299" t="s">
+        <v>452</v>
       </c>
       <c r="H299">
         <v>24.4</v>
@@ -15233,8 +15257,8 @@
       <c r="D300">
         <v>14.9986</v>
       </c>
-      <c r="F300">
-        <v>6</v>
+      <c r="F300" t="s">
+        <v>453</v>
       </c>
       <c r="H300">
         <v>27</v>
@@ -15274,8 +15298,8 @@
       <c r="D301">
         <v>14.9328</v>
       </c>
-      <c r="F301">
-        <v>6</v>
+      <c r="F301" t="s">
+        <v>453</v>
       </c>
       <c r="H301">
         <v>25.5</v>
@@ -15321,8 +15345,8 @@
       <c r="E302">
         <v>78</v>
       </c>
-      <c r="F302">
-        <v>6</v>
+      <c r="F302" t="s">
+        <v>453</v>
       </c>
       <c r="H302">
         <v>32</v>
@@ -15365,8 +15389,8 @@
       <c r="D303">
         <v>13.8937</v>
       </c>
-      <c r="F303">
-        <v>6</v>
+      <c r="F303" t="s">
+        <v>453</v>
       </c>
       <c r="H303">
         <v>5.9</v>
@@ -15406,8 +15430,8 @@
       <c r="D304">
         <v>13.9845</v>
       </c>
-      <c r="F304">
-        <v>6</v>
+      <c r="F304" t="s">
+        <v>453</v>
       </c>
       <c r="H304">
         <v>5.95</v>
@@ -15447,8 +15471,8 @@
       <c r="D305">
         <v>14.0392</v>
       </c>
-      <c r="F305">
-        <v>6</v>
+      <c r="F305" t="s">
+        <v>453</v>
       </c>
       <c r="H305">
         <v>6.7</v>
@@ -15488,8 +15512,8 @@
       <c r="D306">
         <v>14.0604</v>
       </c>
-      <c r="F306">
-        <v>6</v>
+      <c r="F306" t="s">
+        <v>453</v>
       </c>
       <c r="H306">
         <v>7.6</v>
@@ -15529,8 +15553,8 @@
       <c r="D307">
         <v>14.2822</v>
       </c>
-      <c r="F307">
-        <v>6</v>
+      <c r="F307" t="s">
+        <v>453</v>
       </c>
       <c r="H307">
         <v>7.050000000000002</v>
@@ -15570,8 +15594,8 @@
       <c r="D308">
         <v>14.5992</v>
       </c>
-      <c r="F308">
-        <v>5</v>
+      <c r="F308" t="s">
+        <v>459</v>
       </c>
       <c r="H308">
         <v>7.4</v>
@@ -15608,8 +15632,8 @@
       <c r="D309">
         <v>14.6456</v>
       </c>
-      <c r="F309">
-        <v>6</v>
+      <c r="F309" t="s">
+        <v>453</v>
       </c>
       <c r="H309">
         <v>7.4</v>
@@ -15649,8 +15673,8 @@
       <c r="D310">
         <v>14.7128</v>
       </c>
-      <c r="F310">
-        <v>6</v>
+      <c r="F310" t="s">
+        <v>453</v>
       </c>
       <c r="H310">
         <v>7.9</v>
@@ -15690,8 +15714,8 @@
       <c r="D311">
         <v>14.6061</v>
       </c>
-      <c r="F311">
-        <v>1</v>
+      <c r="F311" t="s">
+        <v>452</v>
       </c>
       <c r="H311">
         <v>5.5</v>
@@ -15734,8 +15758,8 @@
       <c r="D312">
         <v>11.74108887</v>
       </c>
-      <c r="F312">
-        <v>1</v>
+      <c r="F312" t="s">
+        <v>452</v>
       </c>
       <c r="H312">
         <v>19.05</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/before_conversion_alps_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/before_conversion_alps_mapped_readable.xlsx
@@ -1387,7 +1387,7 @@
     <t>Basalt</t>
   </si>
   <si>
-    <t>Syenite</t>
+    <t>Salt</t>
   </si>
   <si>
     <t>Breccia</t>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/before_conversion_alps_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/before_conversion_alps_mapped_readable.xlsx
@@ -15764,6 +15764,9 @@
       <c r="H312">
         <v>19.05</v>
       </c>
+      <c r="AD312">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
